--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
@@ -1398,7 +1398,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1628,13 +1628,13 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5175,28 +5175,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="U19" t="n">
         <v>2.3</v>
@@ -5268,31 +5268,31 @@
         <v>60</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO19" t="n">
         <v>19.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -5301,7 +5301,7 @@
         <v>7.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
         <v>18.5</v>
@@ -5310,28 +5310,28 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BG19" t="n">
         <v>13</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>3.85</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="H27" t="n">
         <v>2.14</v>
       </c>
       <c r="I27" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7718,10 +7718,10 @@
         <v>1.83</v>
       </c>
       <c r="G29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I29" t="n">
         <v>6.6</v>
@@ -7748,7 +7748,7 @@
         <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -8226,16 +8226,16 @@
         <v>2.68</v>
       </c>
       <c r="G31" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J31" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K31" t="n">
         <v>3.25</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
         <v>1.43</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.55</v>
+        <v>1.9</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="J33" t="n">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="K33" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G34" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
         <v>2.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9045,10 +9045,10 @@
         <v>27</v>
       </c>
       <c r="Z34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA34" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB34" t="n">
         <v>11</v>
@@ -9057,10 +9057,10 @@
         <v>12</v>
       </c>
       <c r="AD34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE34" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF34" t="n">
         <v>12</v>
@@ -9072,7 +9072,7 @@
         <v>24</v>
       </c>
       <c r="AI34" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="n">
         <v>17.5</v>
@@ -9081,70 +9081,70 @@
         <v>18.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM34" t="n">
         <v>120</v>
       </c>
       <c r="AN34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO34" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP34" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="AZ34" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF34" t="n">
         <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -9242,19 +9242,19 @@
         <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H35" t="n">
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J35" t="n">
         <v>1.01</v>
       </c>
       <c r="K35" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -9496,10 +9496,10 @@
         <v>2.12</v>
       </c>
       <c r="G36" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I36" t="n">
         <v>4.3</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q38" t="n">
         <v>2.72</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="G39" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="H39" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="I39" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K39" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>1.44</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>1.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
         <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
         <v>2.3</v>
@@ -5283,13 +5283,13 @@
         <v>19.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
         <v>4.7</v>
@@ -5298,10 +5298,10 @@
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
         <v>18.5</v>
@@ -5310,10 +5310,10 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
         <v>4.7</v>
@@ -5331,7 +5331,7 @@
         <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG19" t="n">
         <v>13</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7210,16 +7210,16 @@
         <v>3.85</v>
       </c>
       <c r="G27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H27" t="n">
         <v>2.14</v>
       </c>
       <c r="I27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
         <v>3.6</v>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q27" t="n">
         <v>2.18</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K28" t="n">
         <v>3.1</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7718,16 +7718,16 @@
         <v>1.83</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
         <v>6.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K29" t="n">
         <v>3.75</v>
@@ -7748,7 +7748,7 @@
         <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -8226,16 +8226,16 @@
         <v>2.68</v>
       </c>
       <c r="G31" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K31" t="n">
         <v>3.25</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -8477,28 +8477,28 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H32" t="n">
         <v>3.15</v>
       </c>
-      <c r="H32" t="n">
-        <v>2.78</v>
-      </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="K32" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -8988,19 +8988,19 @@
         <v>1.58</v>
       </c>
       <c r="G34" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
         <v>6.6</v>
       </c>
       <c r="J34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9120,7 +9120,7 @@
         <v>3.75</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="AZ34" t="n">
         <v>4.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
         <v>1.71</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -9753,13 +9753,13 @@
         <v>2.48</v>
       </c>
       <c r="H37" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I37" t="n">
         <v>4.5</v>
       </c>
       <c r="J37" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K37" t="n">
         <v>3.1</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3914,10 +3914,10 @@
         <v>3.05</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.4</v>
@@ -3938,7 +3938,7 @@
         <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
         <v>1.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>3.85</v>
       </c>
       <c r="G27" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H27" t="n">
         <v>2.14</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7721,16 +7721,16 @@
         <v>1.95</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J31" t="n">
         <v>2.94</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="H32" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="J32" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
         <v>1.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q33" t="n">
         <v>2.42</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
         <v>5.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG34" t="n">
         <v>5.2</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="H38" t="n">
-        <v>3.95</v>
+        <v>1.59</v>
       </c>
       <c r="I38" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
         <v>2.54</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q38" t="n">
         <v>2.72</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
         <v>1.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.13</v>
+        <v>2.72</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB39"/>
+  <dimension ref="A1:CB43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,212 +875,212 @@
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -1129,219 +1129,219 @@
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:15:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.89</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>1.46</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,244 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skovde AIK</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Stockholm Internazionale</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Skovde AIK</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,37 +3642,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>FC Stockholm Internazionale</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,37 +4150,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1.67</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,37 +4404,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4</v>
+        <v>2.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,42 +4907,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,42 +5161,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5217,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5229,112 +5229,112 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,33 +5415,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="K20" t="n">
         <v>3.5</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,36 +5669,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CA Puerto Nuevo</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,27 +5923,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CSD Central Ballester</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,42 +6177,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Club Lujan</t>
+          <t>Deportes Concepcion</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CSD Yupanqui</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6233,10 +6233,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -6245,112 +6245,112 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CA Claypole</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="H24" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Juventud Unida San Miguel</t>
+          <t>CA Puerto Nuevo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Estrella del Sur</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>CSD Central Ballester</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Mercedes</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Club Lujan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>CSD Yupanqui</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,42 +7447,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,42 +7701,42 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Juventud Unida San Miguel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Estrella del Sur</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,27 +7955,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Club Mercedes</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="G31" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J31" t="n">
         <v>2.94</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,42 +8463,42 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H32" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="I32" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,42 +8717,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="H33" t="n">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,42 +8971,42 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>1.63</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="K34" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9027,10 +9027,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -9039,112 +9039,112 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,42 +9225,42 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,42 +9479,42 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="H36" t="n">
-        <v>3.65</v>
+        <v>2.32</v>
       </c>
       <c r="I36" t="n">
-        <v>4.3</v>
+        <v>2.64</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="K36" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,42 +9733,42 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.28</v>
+        <v>4.3</v>
       </c>
       <c r="G37" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>3.9</v>
+        <v>1.86</v>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="J37" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.1</v>
+        <v>500</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,67 +9987,67 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U38" t="n">
         <v>2.08</v>
       </c>
-      <c r="G38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
@@ -10055,112 +10055,112 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH38" t="n">
         <v>0</v>
@@ -10224,14 +10224,14 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,244 +10241,1260 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G39" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H39" t="n">
         <v>3.6</v>
       </c>
       <c r="I39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:58:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:58:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:58:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:58:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I43" t="n">
         <v>4.7</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J43" t="n">
         <v>2.96</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K43" t="n">
         <v>3.2</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB39" t="inlineStr">
-        <is>
-          <t>2026-06-12 07:41:10</t>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB43" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB51"/>
+  <dimension ref="A1:CB53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.14</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1395,16 +1395,16 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.7</v>
@@ -1413,7 +1413,7 @@
         <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
         <v>1.35</v>
@@ -1473,10 +1473,10 @@
         <v>16.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>3.85</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I5" t="n">
         <v>1.55</v>
@@ -1634,121 +1634,121 @@
         <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>1.01</v>
@@ -1757,7 +1757,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
         <v>1.01</v>
@@ -1778,71 +1778,71 @@
         <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
@@ -1891,13 +1891,13 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
@@ -1906,22 +1906,22 @@
         <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
         <v>1.96</v>
@@ -1948,22 +1948,22 @@
         <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
@@ -1981,7 +1981,7 @@
         <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>12</v>
@@ -1993,7 +1993,7 @@
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
@@ -2020,7 +2020,7 @@
         <v>16</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
         <v>1.01</v>
@@ -2038,19 +2038,19 @@
         <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
@@ -2062,41 +2062,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -2384,31 +2384,31 @@
         <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>2.18</v>
@@ -2423,22 +2423,22 @@
         <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
         <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
         <v>27</v>
@@ -2447,25 +2447,25 @@
         <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
         <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>44</v>
@@ -2474,7 +2474,7 @@
         <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
@@ -2489,122 +2489,122 @@
         <v>28</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF8" t="n">
         <v>12</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11.5</v>
       </c>
       <c r="BG8" t="n">
         <v>18</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="G9" t="n">
         <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2665,10 +2665,10 @@
         <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
@@ -2692,7 +2692,7 @@
         <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
@@ -2704,7 +2704,7 @@
         <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
         <v>20</v>
@@ -2722,7 +2722,7 @@
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
         <v>26</v>
@@ -2731,13 +2731,13 @@
         <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>60</v>
@@ -2749,13 +2749,13 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2764,7 +2764,7 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
         <v>9.800000000000001</v>
@@ -2773,10 +2773,10 @@
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>40</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
         <v>17</v>
@@ -2785,87 +2785,87 @@
         <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
         <v>9.4</v>
       </c>
       <c r="BG9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV9" t="n">
         <v>36</v>
       </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2901,46 +2901,46 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.02</v>
       </c>
-      <c r="K10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3051,10 +3051,10 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3182,7 +3182,7 @@
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3194,7 +3194,7 @@
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q12" t="n">
         <v>1.15</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,16 +3675,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
         <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -3914,19 +3914,19 @@
         <v>1.62</v>
       </c>
       <c r="I14" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
         <v>2.74</v>
@@ -3938,13 +3938,13 @@
         <v>2.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3953,7 +3953,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="W14" t="n">
         <v>1.21</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="G15" t="n">
         <v>2.22</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="I15" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,31 +4183,31 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="O15" t="n">
         <v>1.09</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.32</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.33</v>
       </c>
       <c r="W15" t="n">
         <v>1.81</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
         <v>3.9</v>
@@ -4425,10 +4425,10 @@
         <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4443,16 +4443,16 @@
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
         <v>1.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
         <v>1.43</v>
@@ -4464,7 +4464,7 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
         <v>38</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
         <v>1.99</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -4700,7 +4700,7 @@
         <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.54</v>
@@ -4709,10 +4709,10 @@
         <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
         <v>1.26</v>
@@ -4838,13 +4838,13 @@
         <v>9.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17" t="n">
         <v>5.1</v>
@@ -4856,13 +4856,13 @@
         <v>13</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR17" t="n">
         <v>23</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
         <v>8.199999999999999</v>
@@ -4874,30 +4874,30 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ17" t="n">
         <v>16.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,55 +4912,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>3.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
@@ -5196,10 +5196,10 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.11</v>
@@ -5208,13 +5208,13 @@
         <v>3.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="R19" t="n">
         <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="T19" t="n">
         <v>1.35</v>
@@ -5223,7 +5223,7 @@
         <v>3.15</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
         <v>1.94</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,214 +5420,214 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.44</v>
+        <v>1.22</v>
       </c>
       <c r="G20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>490</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF20" t="n">
         <v>2.64</v>
       </c>
-      <c r="H20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="BG20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI20" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP20" t="n">
         <v>7</v>
       </c>
-      <c r="AU20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS20" t="n">
         <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU20" t="n">
         <v>1.01</v>
@@ -5639,27 +5639,27 @@
         <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY20" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,157 +5674,157 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="G21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.7</v>
       </c>
-      <c r="H21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Q21" t="n">
-        <v>2.74</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>1.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>2.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
         <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB21" t="n">
         <v>1.01</v>
@@ -5842,71 +5842,71 @@
         <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
         <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -5985,10 +5985,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,175 +6182,175 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>1.67</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>1.27</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="P23" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6359,10 +6359,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6371,28 +6371,28 @@
         <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
         <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6407,21 +6407,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
         <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,246 +6436,246 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.7</v>
+        <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="K24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU24" t="n">
         <v>5.2</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X24" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,184 +6690,184 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.22</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
-        <v>1.29</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y25" t="n">
         <v>11.5</v>
       </c>
-      <c r="I25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="Z25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU25" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>490</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS25" t="n">
+      <c r="AV25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>20</v>
-      </c>
       <c r="BA25" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.64</v>
+        <v>5.7</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH25" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
         <v>1.01</v>
@@ -6879,25 +6879,25 @@
         <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
         <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
         <v>1.01</v>
@@ -6915,21 +6915,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,184 +6944,184 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.25</v>
       </c>
-      <c r="P26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S26" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK26" t="n">
         <v>1.01</v>
@@ -7133,13 +7133,13 @@
         <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
         <v>1.01</v>
@@ -7151,7 +7151,7 @@
         <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -7207,46 +7207,46 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
         <v>2.42</v>
       </c>
       <c r="I27" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
         <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -7255,10 +7255,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,175 +7452,175 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
         <v>1.04</v>
       </c>
-      <c r="G28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -7706,31 +7706,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="K29" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,22 +7739,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O29" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
         <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7766,7 +7766,7 @@
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,55 +7960,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.8</v>
+        <v>1.06</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="R30" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -8017,10 +8017,10 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8092,7 +8092,7 @@
         <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
         <v>1.01</v>
@@ -8107,7 +8107,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
         <v>1.01</v>
@@ -8122,7 +8122,7 @@
         <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I31" t="n">
         <v>2.48</v>
@@ -8241,16 +8241,16 @@
         <v>3.95</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P31" t="n">
         <v>2.08</v>
@@ -8259,10 +8259,10 @@
         <v>1.81</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
         <v>1.69</v>
@@ -8271,10 +8271,10 @@
         <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X31" t="n">
         <v>21</v>
@@ -8307,25 +8307,25 @@
         <v>15.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ31" t="n">
         <v>60</v>
       </c>
       <c r="AK31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO31" t="n">
         <v>19.5</v>
@@ -8340,7 +8340,7 @@
         <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT31" t="n">
         <v>10.5</v>
@@ -8361,22 +8361,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB31" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB31" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC31" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BD31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE31" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5</v>
       </c>
       <c r="BF31" t="n">
         <v>21</v>
@@ -8385,75 +8385,75 @@
         <v>13</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,251 +8463,251 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="G32" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="H32" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2.72</v>
+        <v>4.7</v>
       </c>
       <c r="K32" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P32" t="n">
-        <v>1.44</v>
+        <v>2.78</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,251 +8717,251 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Mercedes</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.02</v>
+        <v>2.64</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H33" t="n">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CA Claypole</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H34" t="n">
-        <v>1.02</v>
+        <v>2.36</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9230,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Juventud Unida San Miguel</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estrella del Sur</t>
+          <t>Club Mercedes</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Club Lujan</t>
+          <t>Juventud Unida San Miguel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSD Yupanqui</t>
+          <t>Estrella del Sur</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CA Puerto Nuevo</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -10224,14 +10224,14 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,27 +10241,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>CA Puerto Nuevo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
@@ -10478,14 +10478,14 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10495,42 +10495,42 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Lujan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>CSD Yupanqui</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.6</v>
+        <v>1.02</v>
       </c>
       <c r="G40" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="I40" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>2.94</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10754,37 +10754,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>2.86</v>
+        <v>1.02</v>
       </c>
       <c r="K41" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -10793,10 +10793,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -10986,14 +10986,14 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11008,37 +11008,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="G42" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="H42" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="I42" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="K42" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11240,14 +11240,14 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11262,37 +11262,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H43" t="n">
         <v>3.85</v>
       </c>
-      <c r="G43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2.14</v>
-      </c>
       <c r="I43" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="K43" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
@@ -11511,42 +11511,42 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.75</v>
+        <v>1.83</v>
       </c>
       <c r="G44" t="n">
-        <v>4.3</v>
+        <v>1.95</v>
       </c>
       <c r="H44" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="I44" t="n">
-        <v>2.52</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="K44" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -11555,10 +11555,10 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -11748,14 +11748,14 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11765,36 +11765,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="F45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G45" t="n">
         <v>4.3</v>
       </c>
-      <c r="G45" t="n">
-        <v>1000</v>
-      </c>
       <c r="H45" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="I45" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="J45" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K45" t="n">
-        <v>500</v>
+        <v>3.6</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11809,10 +11809,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -12002,14 +12002,14 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12019,42 +12019,42 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="G46" t="n">
-        <v>1.63</v>
+        <v>4.3</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="I46" t="n">
-        <v>6.6</v>
+        <v>2.52</v>
       </c>
       <c r="J46" t="n">
-        <v>4.4</v>
+        <v>2.76</v>
       </c>
       <c r="K46" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -12087,112 +12087,112 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BH46" t="n">
         <v>0</v>
@@ -12256,14 +12256,14 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12273,36 +12273,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="I47" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="J47" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -12317,10 +12317,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -12510,14 +12510,14 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12527,42 +12527,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="G48" t="n">
-        <v>2.36</v>
+        <v>1.63</v>
       </c>
       <c r="H48" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J48" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="K48" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -12571,10 +12571,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.71</v>
+        <v>2.22</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -12583,10 +12583,10 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -12595,112 +12595,112 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH48" t="n">
         <v>0</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,37 +12786,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>2.86</v>
+        <v>1.02</v>
       </c>
       <c r="K49" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -12825,10 +12825,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -13018,14 +13018,14 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13035,42 +13035,42 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="H50" t="n">
-        <v>1.59</v>
+        <v>3.6</v>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,261 +13272,769 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-12 12:17:49</t>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB51" t="inlineStr">
+        <is>
+          <t>2026-06-12 14:36:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>19:30:00</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB52" t="inlineStr">
+        <is>
+          <t>2026-06-12 14:36:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Floresta EC</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Figueirense</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="F53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G53" t="n">
         <v>2.44</v>
       </c>
-      <c r="H51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I51" t="n">
+      <c r="H53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I53" t="n">
         <v>4.7</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J53" t="n">
         <v>2.96</v>
       </c>
-      <c r="K51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB51" t="inlineStr">
-        <is>
-          <t>2026-06-12 12:17:49</t>
+      <c r="K53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB53" t="inlineStr">
+        <is>
+          <t>2026-06-12 14:36:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB53"/>
+  <dimension ref="A1:CB54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.23</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.14</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1395,10 +1395,10 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
@@ -1413,7 +1413,7 @@
         <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W4" t="n">
         <v>1.35</v>
@@ -1494,7 +1494,7 @@
         <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1751,31 +1751,31 @@
         <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
         <v>6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
@@ -1891,7 +1891,7 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1903,7 +1903,7 @@
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
         <v>1.79</v>
@@ -1915,16 +1915,16 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1951,10 +1951,10 @@
         <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
@@ -1963,7 +1963,7 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
@@ -1975,7 +1975,7 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>60</v>
@@ -1987,7 +1987,7 @@
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
@@ -1996,13 +1996,13 @@
         <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -2023,7 +2023,7 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
         <v>1.01</v>
@@ -2038,19 +2038,19 @@
         <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
@@ -2068,13 +2068,13 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT6" t="n">
         <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
         <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="BN8" t="n">
         <v>5.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
         <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.800000000000001</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
         <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
         <v>1.16</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.22</v>
@@ -3182,7 +3182,7 @@
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3191,7 +3191,7 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3675,16 +3675,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -3699,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
         <v>1.62</v>
       </c>
       <c r="I14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="J14" t="n">
         <v>3.65</v>
@@ -3938,7 +3938,7 @@
         <v>2.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R14" t="n">
         <v>1.66</v>
@@ -3947,16 +3947,16 @@
         <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
         <v>2.22</v>
       </c>
       <c r="H15" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,94 +4183,94 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="R15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S15" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
         <v>1.81</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR15" t="n">
         <v>1.01</v>
@@ -4279,46 +4279,46 @@
         <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BE15" t="n">
         <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
         <v>4.7</v>
@@ -4431,7 +4431,7 @@
         <v>5.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -4464,7 +4464,7 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
         <v>38</v>
@@ -4575,58 +4575,58 @@
         <v>19</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G17" t="n">
         <v>1.99</v>
@@ -4700,19 +4700,19 @@
         <v>2.38</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.54</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.6</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
         <v>1.26</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,157 +4912,157 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.36</v>
+        <v>4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="J18" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
         <v>5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.14</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
         <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>1.01</v>
@@ -5080,71 +5080,71 @@
         <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
         <v>2.06</v>
@@ -5193,7 +5193,7 @@
         <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -5205,19 +5205,19 @@
         <v>1.11</v>
       </c>
       <c r="P19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R19" t="n">
         <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U19" t="n">
         <v>3.15</v>
@@ -5244,7 +5244,7 @@
         <v>25</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD19" t="n">
         <v>21</v>
@@ -5337,13 +5337,13 @@
         <v>11.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK19" t="n">
         <v>1.01</v>
@@ -5355,10 +5355,10 @@
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5373,7 +5373,7 @@
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU19" t="n">
         <v>1.01</v>
@@ -5391,14 +5391,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA19" t="n">
         <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,157 +5674,157 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.7</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>5.5</v>
+        <v>2.58</v>
       </c>
       <c r="H21" t="n">
-        <v>1.62</v>
+        <v>2.76</v>
       </c>
       <c r="I21" t="n">
-        <v>1.75</v>
+        <v>3.55</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.69</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="V21" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="X21" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
         <v>22</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AI21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
         <v>34</v>
       </c>
-      <c r="AC21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AL21" t="n">
         <v>55</v>
       </c>
-      <c r="AG21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="n">
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
         <v>32</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>48</v>
-      </c>
       <c r="AO21" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
         <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
         <v>1.01</v>
@@ -5842,71 +5842,71 @@
         <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5970,13 +5970,13 @@
         <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,13 +6215,13 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O23" t="n">
         <v>1.24</v>
       </c>
       <c r="P23" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q23" t="n">
         <v>1.24</v>
@@ -6230,7 +6230,7 @@
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6699,40 +6699,40 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K25" t="n">
         <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
         <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P25" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
         <v>1.26</v>
@@ -6741,16 +6741,16 @@
         <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X25" t="n">
         <v>12</v>
@@ -6813,7 +6813,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AS25" t="n">
         <v>5.7</v>
@@ -6822,7 +6822,7 @@
         <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AV25" t="n">
         <v>11</v>
@@ -6846,7 +6846,7 @@
         <v>5.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BD25" t="n">
         <v>5.7</v>
@@ -6855,74 +6855,74 @@
         <v>6</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG25" t="n">
         <v>5.6</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G26" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
@@ -7004,10 +7004,10 @@
         <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X26" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
         <v>21</v>
@@ -7022,7 +7022,7 @@
         <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
         <v>38</v>
@@ -7067,10 +7067,10 @@
         <v>16.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AT26" t="n">
         <v>5.6</v>
@@ -7079,10 +7079,10 @@
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AW26" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -7094,7 +7094,7 @@
         <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BB26" t="n">
         <v>12.5</v>
@@ -7106,13 +7106,13 @@
         <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BF26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BH26" t="n">
         <v>3.2</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7210,56 +7210,56 @@
         <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H27" t="n">
         <v>2.42</v>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
         <v>4.4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.45</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.44</v>
-      </c>
       <c r="X27" t="n">
         <v>1000</v>
       </c>
@@ -7369,13 +7369,13 @@
         <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
         <v>1.01</v>
@@ -7387,10 +7387,10 @@
         <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
@@ -7405,10 +7405,10 @@
         <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
         <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
@@ -7491,7 +7491,7 @@
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
         <v>1.65</v>
@@ -7536,7 +7536,7 @@
         <v>16</v>
       </c>
       <c r="AE28" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF28" t="n">
         <v>20</v>
@@ -7548,16 +7548,16 @@
         <v>18</v>
       </c>
       <c r="AI28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ28" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
         <v>26</v>
       </c>
       <c r="AL28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM28" t="n">
         <v>75</v>
@@ -7578,7 +7578,7 @@
         <v>18.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
         <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
@@ -7602,19 +7602,19 @@
         <v>12</v>
       </c>
       <c r="BA28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB28" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.5</v>
       </c>
       <c r="BC28" t="n">
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF28" t="n">
         <v>10.5</v>
@@ -7623,68 +7623,68 @@
         <v>17.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK28" t="n">
         <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM28" t="n">
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ28" t="n">
         <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS28" t="n">
         <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW28" t="n">
         <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY28" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA28" t="n">
         <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7739,22 +7739,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P29" t="n">
         <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7763,7 +7763,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
         <v>1.58</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -8002,7 +8002,7 @@
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8235,22 +8235,22 @@
         <v>2.48</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K31" t="n">
         <v>3.95</v>
       </c>
       <c r="L31" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P31" t="n">
         <v>2.08</v>
@@ -8259,10 +8259,10 @@
         <v>1.81</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
         <v>1.69</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
         <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="O32" t="n">
         <v>1.09</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8755,28 +8755,28 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="O33" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P33" t="n">
         <v>2.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="S33" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="V33" t="n">
         <v>1.61</v>
@@ -8785,100 +8785,100 @@
         <v>1.52</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS33" t="n">
         <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB33" t="n">
         <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD33" t="n">
         <v>1.01</v>
@@ -8887,10 +8887,10 @@
         <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8985,230 +8985,230 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="G34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K34" t="n">
         <v>3.6</v>
       </c>
-      <c r="H34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8.6</v>
-      </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P34" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9230,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>CA Puerto Nuevo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Mercedes</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -9257,16 +9257,16 @@
         <v>1000</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P35" t="n">
         <v>1.24</v>
@@ -9275,184 +9275,184 @@
         <v>1.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Juventud Unida San Miguel</t>
+          <t>CSD Central Ballester</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Estrella del Sur</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -9505,22 +9505,22 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P36" t="n">
         <v>1.24</v>
@@ -9529,184 +9529,184 @@
         <v>1.01</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CA Claypole</t>
+          <t>Club Lujan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>CSD Yupanqui</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -9765,16 +9765,16 @@
         <v>1000</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P37" t="n">
         <v>1.24</v>
@@ -9783,184 +9783,184 @@
         <v>1.01</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9992,12 +9992,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CSD Central Ballester</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -10019,16 +10019,16 @@
         <v>1000</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P38" t="n">
         <v>1.24</v>
@@ -10037,194 +10037,194 @@
         <v>1.01</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10246,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CA Puerto Nuevo</t>
+          <t>Juventud Unida San Miguel</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>Estrella del Sur</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -10273,16 +10273,16 @@
         <v>1000</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P39" t="n">
         <v>1.24</v>
@@ -10291,194 +10291,194 @@
         <v>1.01</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -10500,12 +10500,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Club Lujan</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CSD Yupanqui</t>
+          <t>Club Mercedes</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -10527,16 +10527,16 @@
         <v>1000</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P40" t="n">
         <v>1.24</v>
@@ -10545,184 +10545,184 @@
         <v>1.01</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
         <v>0</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10754,246 +10754,246 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H41" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J41" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11008,246 +11008,246 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84</v>
+        <v>2.34</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I42" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="J42" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P42" t="n">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.58</v>
+        <v>1.87</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP42" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR42" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV42" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11262,246 +11262,246 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="G43" t="n">
-        <v>2.46</v>
+        <v>4.3</v>
       </c>
       <c r="H43" t="n">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="I43" t="n">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="J43" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="K43" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI43" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11516,246 +11516,246 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="G44" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="H44" t="n">
-        <v>4.4</v>
+        <v>1.12</v>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O44" t="n">
         <v>1.09</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
       <c r="P44" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11770,239 +11770,239 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H45" t="n">
         <v>3.85</v>
       </c>
-      <c r="G45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2.14</v>
-      </c>
       <c r="I45" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="K45" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P45" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="Q45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
         <v>2.22</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BH45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -12019,251 +12019,251 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.6</v>
+        <v>1.76</v>
       </c>
       <c r="G46" t="n">
-        <v>4.3</v>
+        <v>1.91</v>
       </c>
       <c r="H46" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="I46" t="n">
-        <v>2.52</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="K46" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P46" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI46" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12273,251 +12273,251 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G47" t="n">
         <v>4.3</v>
       </c>
-      <c r="G47" t="n">
-        <v>1000</v>
-      </c>
       <c r="H47" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="I47" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="J47" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="K47" t="n">
-        <v>500</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12527,42 +12527,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.57</v>
+        <v>4.3</v>
       </c>
       <c r="G48" t="n">
-        <v>1.63</v>
+        <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>1.86</v>
       </c>
       <c r="I48" t="n">
-        <v>6.8</v>
+        <v>2.12</v>
       </c>
       <c r="J48" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="K48" t="n">
-        <v>4.8</v>
+        <v>500</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -12571,10 +12571,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -12583,10 +12583,10 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -12595,112 +12595,112 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BH48" t="n">
         <v>0</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12781,42 +12781,42 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G49" t="n">
-        <v>1000</v>
+        <v>1.63</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -12825,10 +12825,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -12837,10 +12837,10 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -12849,112 +12849,112 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -13272,14 +13272,14 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13294,37 +13294,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="G51" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>2.86</v>
+        <v>1.02</v>
       </c>
       <c r="K51" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -13333,10 +13333,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -13526,14 +13526,14 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13543,42 +13543,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H52" t="n">
-        <v>1.72</v>
+        <v>3.95</v>
       </c>
       <c r="I52" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="K52" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -13587,10 +13587,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -13802,239 +13802,493 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB53" t="inlineStr">
+        <is>
+          <t>2026-06-12 16:55:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Floresta EC</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Figueirense</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB53" t="inlineStr">
-        <is>
-          <t>2026-06-12 14:36:19</t>
+      <c r="F54" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB54" t="inlineStr">
+        <is>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.23</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G4" t="n">
         <v>3.95</v>
@@ -1398,7 +1398,7 @@
         <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
@@ -1425,7 +1425,7 @@
         <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
         <v>32</v>
@@ -1455,7 +1455,7 @@
         <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK4" t="n">
         <v>55</v>
@@ -1467,7 +1467,7 @@
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO4" t="n">
         <v>16.5</v>
@@ -1482,19 +1482,19 @@
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1524,7 +1524,7 @@
         <v>3.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
         <v>4.2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1936,10 +1936,10 @@
         <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
@@ -1951,7 +1951,7 @@
         <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1963,22 +1963,22 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>12.5</v>
@@ -1993,10 +1993,10 @@
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>12.5</v>
@@ -2008,7 +2008,7 @@
         <v>9.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>12.5</v>
@@ -2017,10 +2017,10 @@
         <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
@@ -2029,74 +2029,74 @@
         <v>1.01</v>
       </c>
       <c r="BF6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>9</v>
       </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BT6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
         <v>2.98</v>
@@ -2405,22 +2405,22 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T8" t="n">
         <v>1.55</v>
@@ -2444,7 +2444,7 @@
         <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
         <v>15</v>
@@ -2486,7 +2486,7 @@
         <v>18</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP8" t="n">
         <v>5.1</v>
@@ -2495,16 +2495,16 @@
         <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2513,7 +2513,7 @@
         <v>5.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
         <v>9</v>
@@ -2540,43 +2540,43 @@
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BN8" t="n">
         <v>5.7</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BO8" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
@@ -2671,64 +2671,64 @@
         <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
         <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK9" t="n">
         <v>20</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>34</v>
@@ -2737,37 +2737,37 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>9</v>
@@ -2776,34 +2776,34 @@
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK9" t="n">
         <v>5</v>
@@ -2815,31 +2815,31 @@
         <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BP9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS9" t="n">
         <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
         <v>8</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>22</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2919,7 +2919,7 @@
         <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.16</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.22</v>
@@ -3182,7 +3182,7 @@
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3424,19 +3424,19 @@
         <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
         <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.19</v>
@@ -3759,52 +3759,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G14" t="n">
         <v>6.2</v>
@@ -3962,16 +3962,16 @@
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC14" t="n">
         <v>1000</v>
@@ -3980,7 +3980,7 @@
         <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF14" t="n">
         <v>1000</v>
@@ -3989,7 +3989,7 @@
         <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -4180,10 +4180,10 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.12</v>
@@ -4273,7 +4273,7 @@
         <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
         <v>1.95</v>
@@ -4428,7 +4428,7 @@
         <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
@@ -4521,7 +4521,7 @@
         <v>32</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
         <v>18</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -4658,187 +4658,187 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.84</v>
+        <v>2.72</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="H17" t="n">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>2.76</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AB17" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,50 +4847,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BP17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
         <v>2.16</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U18" t="n">
         <v>2.44</v>
@@ -5047,7 +5047,7 @@
         <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW18" t="n">
         <v>11.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G19" t="n">
         <v>2.06</v>
@@ -5208,7 +5208,7 @@
         <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R19" t="n">
         <v>2.02</v>
@@ -5286,7 +5286,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
         <v>1.01</v>
@@ -5304,7 +5304,7 @@
         <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
         <v>15.5</v>
@@ -5316,10 +5316,10 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
         <v>13.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -5465,10 +5465,10 @@
         <v>1.29</v>
       </c>
       <c r="R20" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="T20" t="n">
         <v>1.74</v>
@@ -5600,13 +5600,13 @@
         <v>12</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5624,25 +5624,25 @@
         <v>18</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT20" t="n">
         <v>16</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX20" t="n">
         <v>65</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>2.58</v>
       </c>
       <c r="H21" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I21" t="n">
         <v>3.55</v>
@@ -5725,7 +5725,7 @@
         <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
         <v>1.98</v>
@@ -5791,58 +5791,58 @@
         <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6045,52 +6045,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,13 +6215,13 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.24</v>
       </c>
       <c r="P23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q23" t="n">
         <v>1.24</v>
@@ -6299,52 +6299,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
         <v>2.66</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BJ24" t="n">
         <v>12.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
         <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
         <v>1.85</v>
@@ -6750,7 +6750,7 @@
         <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>12</v>
@@ -6813,7 +6813,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS25" t="n">
         <v>5.7</v>
@@ -6822,7 +6822,7 @@
         <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AV25" t="n">
         <v>11</v>
@@ -6843,10 +6843,10 @@
         <v>5.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD25" t="n">
         <v>5.7</v>
@@ -6855,7 +6855,7 @@
         <v>6</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG25" t="n">
         <v>5.6</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
         <v>4.4</v>
@@ -7004,7 +7004,7 @@
         <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X26" t="n">
         <v>14</v>
@@ -7124,13 +7124,13 @@
         <v>13</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN26" t="n">
         <v>3.95</v>
@@ -7142,41 +7142,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26" t="n">
         <v>11.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -7198,239 +7198,239 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.72</v>
+        <v>1.82</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>1.99</v>
       </c>
       <c r="H27" t="n">
-        <v>2.42</v>
+        <v>3.95</v>
       </c>
       <c r="I27" t="n">
-        <v>2.76</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="n">
         <v>4.4</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BI27" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BJ27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN27" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU27" t="n">
         <v>6</v>
       </c>
-      <c r="BU27" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>2.42</v>
       </c>
       <c r="H28" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>3.35</v>
@@ -7527,7 +7527,7 @@
         <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
@@ -7539,7 +7539,7 @@
         <v>34</v>
       </c>
       <c r="AF28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG28" t="n">
         <v>13.5</v>
@@ -7578,7 +7578,7 @@
         <v>18.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
         <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
@@ -7602,19 +7602,19 @@
         <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF28" t="n">
         <v>10.5</v>
@@ -7632,13 +7632,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL28" t="n">
         <v>90</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN28" t="n">
         <v>5.7</v>
@@ -7650,16 +7650,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR28" t="n">
         <v>26</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU28" t="n">
         <v>5.2</v>
@@ -7668,23 +7668,23 @@
         <v>24</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX28" t="n">
         <v>32</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ28" t="n">
         <v>19.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O29" t="n">
         <v>1.02</v>
@@ -7823,52 +7823,52 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -8002,7 +8002,7 @@
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -8077,52 +8077,52 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -8394,59 +8394,59 @@
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -8486,10 +8486,10 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K32" t="n">
         <v>5.4</v>
@@ -8501,7 +8501,7 @@
         <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O32" t="n">
         <v>1.09</v>
@@ -8525,7 +8525,7 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
         <v>2.2</v>
@@ -8585,52 +8585,52 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>2.64</v>
       </c>
       <c r="G33" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H33" t="n">
         <v>2.38</v>
@@ -8782,7 +8782,7 @@
         <v>1.61</v>
       </c>
       <c r="W33" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X33" t="n">
         <v>34</v>
@@ -8848,7 +8848,7 @@
         <v>16</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT33" t="n">
         <v>14</v>
@@ -8875,16 +8875,16 @@
         <v>21</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC33" t="n">
         <v>19.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF33" t="n">
         <v>11</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -9009,16 +9009,16 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="O34" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P34" t="n">
         <v>1.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R34" t="n">
         <v>1.16</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="O38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -10763,16 +10763,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="G41" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="H41" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I41" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>3.1</v>
@@ -10811,10 +10811,10 @@
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W41" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="H42" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>3.3</v>
@@ -11035,7 +11035,7 @@
         <v>3.35</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M42" t="n">
         <v>1.07</v>
@@ -11050,7 +11050,7 @@
         <v>1.97</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R42" t="n">
         <v>1.37</v>
@@ -11065,10 +11065,10 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W42" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X42" t="n">
         <v>16.5</v>
@@ -11137,7 +11137,7 @@
         <v>5.8</v>
       </c>
       <c r="AT42" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU42" t="n">
         <v>6.4</v>
@@ -11173,7 +11173,7 @@
         <v>5.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG42" t="n">
         <v>27</v>
@@ -11182,19 +11182,19 @@
         <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BJ42" t="n">
         <v>13</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BN42" t="n">
         <v>7</v>
@@ -11206,13 +11206,13 @@
         <v>23</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BR42" t="n">
         <v>40</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BT42" t="n">
         <v>9</v>
@@ -11224,23 +11224,23 @@
         <v>38</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BX42" t="n">
         <v>50</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ42" t="n">
         <v>34</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>3.85</v>
       </c>
       <c r="G43" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H43" t="n">
         <v>2.14</v>
@@ -11322,7 +11322,7 @@
         <v>1.75</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11442,59 +11442,59 @@
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN43" t="n">
         <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT43" t="n">
         <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
         <v>1.41</v>
       </c>
       <c r="H44" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
         <v>1.09</v>
@@ -11564,7 +11564,7 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11576,7 +11576,7 @@
         <v>1.06</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -11782,16 +11782,16 @@
         <v>2.22</v>
       </c>
       <c r="G45" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H45" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I45" t="n">
         <v>4.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K45" t="n">
         <v>3.1</v>
@@ -11803,22 +11803,22 @@
         <v>1.14</v>
       </c>
       <c r="N45" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="O45" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="P45" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R45" t="n">
         <v>1.17</v>
       </c>
       <c r="S45" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -11830,7 +11830,7 @@
         <v>1.29</v>
       </c>
       <c r="W45" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -12204,59 +12204,59 @@
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN46" t="n">
         <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="O47" t="n">
         <v>1.11</v>
@@ -12323,10 +12323,10 @@
         <v>2.32</v>
       </c>
       <c r="R47" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="S47" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
         <v>4.3</v>
       </c>
       <c r="G48" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H48" t="n">
         <v>1.86</v>
@@ -12556,215 +12556,215 @@
         <v>3.05</v>
       </c>
       <c r="K48" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P48" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q48" t="n">
         <v>2.44</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -12813,16 +12813,16 @@
         <v>4.8</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P49" t="n">
         <v>2.22</v>
@@ -12831,10 +12831,10 @@
         <v>1.72</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T49" t="n">
         <v>1.81</v>
@@ -12843,10 +12843,10 @@
         <v>2.08</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X49" t="n">
         <v>23</v>
@@ -12957,68 +12957,68 @@
         <v>5</v>
       </c>
       <c r="BH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -13064,215 +13064,215 @@
         <v>3.15</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P50" t="n">
         <v>1.71</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -13303,10 +13303,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="G51" t="n">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="H51" t="n">
         <v>1.04</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G52" t="n">
         <v>2.46</v>
@@ -13566,7 +13566,7 @@
         <v>3.95</v>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>2.86</v>
@@ -13575,212 +13575,212 @@
         <v>3.15</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M52" t="n">
         <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q52" t="n">
         <v>2.7</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G54" t="n">
         <v>2.26</v>
@@ -14074,10 +14074,10 @@
         <v>4.3</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J54" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="K54" t="n">
         <v>3.3</v>
@@ -14098,7 +14098,7 @@
         <v>1.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-12 16:55:08</t>
+          <t>2026-06-12 19:13:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1365,160 +1365,160 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,35 +1643,35 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.41</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X5" t="n">
         <v>1000</v>
       </c>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1909,10 +1909,10 @@
         <v>1.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
@@ -2148,10 +2148,10 @@
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.23</v>
@@ -2175,19 +2175,19 @@
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -2199,10 +2199,10 @@
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -2211,10 +2211,10 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
@@ -2232,125 +2232,125 @@
         <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BE7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG7" t="n">
         <v>3.55</v>
       </c>
-      <c r="AV7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD7" t="n">
+      <c r="BH7" t="n">
+        <v>970</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -2895,13 +2895,13 @@
         <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I10" t="n">
         <v>2.14</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -2913,31 +2913,31 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
         <v>1.69</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W10" t="n">
         <v>1.35</v>
@@ -2964,7 +2964,7 @@
         <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
         <v>36</v>
@@ -2988,13 +2988,13 @@
         <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -3006,7 +3006,7 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT10" t="n">
         <v>11.5</v>
@@ -3030,19 +3030,19 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4</v>
-      </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -3173,13 +3173,13 @@
         <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
         <v>2.98</v>
@@ -3188,7 +3188,7 @@
         <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
         <v>2.8</v>
@@ -3200,7 +3200,7 @@
         <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z11" t="n">
         <v>9.4</v>
@@ -3221,13 +3221,13 @@
         <v>17</v>
       </c>
       <c r="AF11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AG11" t="n">
         <v>32</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>40</v>
@@ -3245,7 +3245,7 @@
         <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AO11" t="n">
         <v>8</v>
@@ -3254,55 +3254,55 @@
         <v>13.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV11" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>5.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BH11" t="n">
         <v>3.85</v>
@@ -3362,11 +3362,11 @@
         <v>17.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3678,7 +3678,7 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3935,37 +3935,37 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z14" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA14" t="n">
         <v>140</v>
@@ -3974,13 +3974,13 @@
         <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
         <v>14</v>
@@ -3989,61 +3989,61 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>23</v>
       </c>
       <c r="AK14" t="n">
         <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
         <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
         <v>1.01</v>
@@ -4061,13 +4061,13 @@
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI14" t="n">
         <v>3</v>
@@ -4076,22 +4076,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO14" t="n">
         <v>4</v>
       </c>
       <c r="BP14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>8.800000000000001</v>
@@ -4100,35 +4100,35 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT14" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
         <v>1.34</v>
@@ -4192,7 +4192,7 @@
         <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
@@ -4330,59 +4330,59 @@
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
@@ -4440,13 +4440,13 @@
         <v>2.66</v>
       </c>
       <c r="O16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
         <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -4458,7 +4458,7 @@
         <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
@@ -4584,59 +4584,59 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BN16" t="n">
         <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
         <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q17" t="n">
         <v>1.37</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -5178,16 +5178,16 @@
         <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H19" t="n">
         <v>2.92</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>1.09</v>
       </c>
       <c r="K19" t="n">
         <v>4.8</v>
@@ -5202,13 +5202,13 @@
         <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
@@ -5226,7 +5226,7 @@
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X19" t="n">
         <v>27</v>
@@ -5340,65 +5340,65 @@
         <v>4.3</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BN19" t="n">
         <v>5.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP19" t="n">
         <v>16</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR19" t="n">
         <v>24</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
         <v>22</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>28</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>17</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
         <v>4.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5686,10 @@
         <v>2.36</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H21" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I21" t="n">
         <v>3.15</v>
@@ -5698,10 +5698,10 @@
         <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5716,7 +5716,7 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
         <v>1.48</v>
@@ -5728,22 +5728,22 @@
         <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V21" t="n">
         <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
         <v>55</v>
@@ -5752,28 +5752,28 @@
         <v>15</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -5782,25 +5782,25 @@
         <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
         <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX21" t="n">
         <v>13.5</v>
@@ -5824,25 +5824,25 @@
         <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC21" t="n">
         <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF21" t="n">
         <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH21" t="n">
         <v>3.95</v>
@@ -5851,7 +5851,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21" t="n">
         <v>5.5</v>
@@ -5860,7 +5860,7 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BN21" t="n">
         <v>5.7</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G22" t="n">
         <v>1.94</v>
@@ -5946,7 +5946,7 @@
         <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>3.75</v>
@@ -6081,7 +6081,7 @@
         <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC22" t="n">
         <v>16.5</v>
@@ -6102,7 +6102,7 @@
         <v>3.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BJ22" t="n">
         <v>10</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>2.02</v>
       </c>
       <c r="H23" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.76</v>
       </c>
       <c r="G24" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H24" t="n">
         <v>3.6</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.21</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
         <v>2.16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O27" t="n">
         <v>1.12</v>
@@ -7246,7 +7246,7 @@
         <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
         <v>1.02</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
@@ -7494,13 +7494,13 @@
         <v>1.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R28" t="n">
         <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
@@ -7739,13 +7739,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.12</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q29" t="n">
         <v>1.12</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -7996,13 +7996,13 @@
         <v>1.32</v>
       </c>
       <c r="O30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P30" t="n">
         <v>1.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R30" t="n">
         <v>1.24</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
         <v>6.2</v>
@@ -8244,7 +8244,7 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
         <v>2.74</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -8510,13 +8510,13 @@
         <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="R32" t="n">
         <v>1.88</v>
       </c>
       <c r="S32" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T32" t="n">
         <v>1.42</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -8761,16 +8761,16 @@
         <v>1.23</v>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
         <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T33" t="n">
         <v>1.59</v>
@@ -8815,7 +8815,7 @@
         <v>15</v>
       </c>
       <c r="AH33" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI33" t="n">
         <v>38</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -9012,13 +9012,13 @@
         <v>1.01</v>
       </c>
       <c r="O34" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P34" t="n">
         <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R34" t="n">
         <v>1.8</v>
@@ -9150,65 +9150,65 @@
         <v>5.4</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ34" t="n">
         <v>9</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT34" t="n">
         <v>5.3</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV34" t="n">
         <v>11</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX34" t="n">
         <v>18.5</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ34" t="n">
         <v>11.5</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <v>3.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="R35" t="n">
         <v>2.02</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>11.5</v>
       </c>
       <c r="I36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
         <v>7.2</v>
@@ -9523,7 +9523,7 @@
         <v>1.1</v>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q36" t="n">
         <v>1.3</v>
@@ -9532,13 +9532,13 @@
         <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="T36" t="n">
         <v>1.74</v>
       </c>
       <c r="U36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V36" t="n">
         <v>1.06</v>
@@ -9550,13 +9550,13 @@
         <v>65</v>
       </c>
       <c r="Y36" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Z36" t="n">
         <v>160</v>
       </c>
       <c r="AA36" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AB36" t="n">
         <v>21</v>
@@ -9568,7 +9568,7 @@
         <v>60</v>
       </c>
       <c r="AE36" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF36" t="n">
         <v>14.5</v>
@@ -9580,7 +9580,7 @@
         <v>34</v>
       </c>
       <c r="AI36" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ36" t="n">
         <v>12</v>
@@ -9589,28 +9589,28 @@
         <v>16.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>3</v>
       </c>
       <c r="AO36" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT36" t="n">
         <v>12</v>
@@ -9619,13 +9619,13 @@
         <v>14</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY36" t="n">
         <v>9.4</v>
@@ -9634,7 +9634,7 @@
         <v>20</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB36" t="n">
         <v>9.800000000000001</v>
@@ -9646,13 +9646,13 @@
         <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF36" t="n">
         <v>2.68</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH36" t="n">
         <v>6.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
         <v>4.4</v>
       </c>
       <c r="K37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.21</v>
@@ -9780,7 +9780,7 @@
         <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R37" t="n">
         <v>1.69</v>
@@ -9789,7 +9789,7 @@
         <v>2.18</v>
       </c>
       <c r="T37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U37" t="n">
         <v>2.46</v>
@@ -9804,16 +9804,16 @@
         <v>36</v>
       </c>
       <c r="Y37" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA37" t="n">
         <v>22</v>
       </c>
       <c r="AB37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC37" t="n">
         <v>14</v>
@@ -9906,7 +9906,7 @@
         <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="n">
         <v>4.9</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>3.95</v>
       </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
         <v>3.8</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.25</v>
+        <v>2.74</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -10509,13 +10509,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G40" t="n">
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
@@ -10533,13 +10533,13 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O40" t="n">
         <v>1.24</v>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q40" t="n">
         <v>1.25</v>
@@ -10548,7 +10548,7 @@
         <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -10787,10 +10787,10 @@
         <v>1.13</v>
       </c>
       <c r="N41" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O41" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P41" t="n">
         <v>1.46</v>
@@ -10817,7 +10817,7 @@
         <v>1.59</v>
       </c>
       <c r="X41" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y41" t="n">
         <v>11</v>
@@ -10898,10 +10898,10 @@
         <v>11</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -11029,25 +11029,25 @@
         <v>3.45</v>
       </c>
       <c r="J42" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K42" t="n">
         <v>3.35</v>
       </c>
       <c r="L42" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
         <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P42" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q42" t="n">
         <v>2.24</v>
@@ -11056,10 +11056,10 @@
         <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U42" t="n">
         <v>1.92</v>
@@ -11098,7 +11098,7 @@
         <v>970</v>
       </c>
       <c r="AG42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH42" t="n">
         <v>21</v>
@@ -11110,7 +11110,7 @@
         <v>44</v>
       </c>
       <c r="AK42" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL42" t="n">
         <v>60</v>
@@ -11119,7 +11119,7 @@
         <v>150</v>
       </c>
       <c r="AN42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO42" t="n">
         <v>55</v>
@@ -11128,25 +11128,25 @@
         <v>8.6</v>
       </c>
       <c r="AQ42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT42" t="n">
         <v>8</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AV42" t="n">
         <v>11</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX42" t="n">
         <v>13.5</v>
@@ -11155,34 +11155,34 @@
         <v>10</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB42" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BC42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD42" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE42" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH42" t="n">
         <v>3</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -11289,10 +11289,10 @@
         <v>4.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
         <v>3</v>
@@ -11304,13 +11304,13 @@
         <v>1.68</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R43" t="n">
         <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T43" t="n">
         <v>2.2</v>
@@ -11343,19 +11343,19 @@
         <v>10.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE43" t="n">
         <v>190</v>
       </c>
       <c r="AF43" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AG43" t="n">
         <v>11</v>
       </c>
       <c r="AH43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI43" t="n">
         <v>180</v>
@@ -11385,10 +11385,10 @@
         <v>16.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT43" t="n">
         <v>5.6</v>
@@ -11397,10 +11397,10 @@
         <v>7.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AW43" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX43" t="n">
         <v>7</v>
@@ -11412,7 +11412,7 @@
         <v>20</v>
       </c>
       <c r="BA43" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB43" t="n">
         <v>12.5</v>
@@ -11424,13 +11424,13 @@
         <v>36</v>
       </c>
       <c r="BE43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF43" t="n">
         <v>9.4</v>
       </c>
       <c r="BG43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH43" t="n">
         <v>3.15</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -11531,10 +11531,10 @@
         <v>2.38</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I44" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J44" t="n">
         <v>3.75</v>
@@ -11543,7 +11543,7 @@
         <v>4.1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
@@ -11573,7 +11573,7 @@
         <v>2.38</v>
       </c>
       <c r="V44" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W44" t="n">
         <v>1.72</v>
@@ -11588,7 +11588,7 @@
         <v>28</v>
       </c>
       <c r="AA44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB44" t="n">
         <v>15</v>
@@ -11606,7 +11606,7 @@
         <v>19.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH44" t="n">
         <v>18</v>
@@ -11618,16 +11618,16 @@
         <v>32</v>
       </c>
       <c r="AK44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM44" t="n">
         <v>75</v>
       </c>
       <c r="AN44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO44" t="n">
         <v>27</v>
@@ -11642,7 +11642,7 @@
         <v>18.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT44" t="n">
         <v>10</v>
@@ -11654,7 +11654,7 @@
         <v>10.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX44" t="n">
         <v>13</v>
@@ -11666,19 +11666,19 @@
         <v>12</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC44" t="n">
         <v>19</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF44" t="n">
         <v>10.5</v>
@@ -11708,13 +11708,13 @@
         <v>5.7</v>
       </c>
       <c r="BO44" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP44" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ44" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BR44" t="n">
         <v>26</v>
@@ -11726,7 +11726,7 @@
         <v>7</v>
       </c>
       <c r="BU44" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV44" t="n">
         <v>24</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -11785,13 +11785,13 @@
         <v>1.44</v>
       </c>
       <c r="H45" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I45" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J45" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K45" t="n">
         <v>5.1</v>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
         <v>1.41</v>
@@ -11818,7 +11818,7 @@
         <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="T45" t="n">
         <v>2.6</v>
@@ -11827,7 +11827,7 @@
         <v>1.52</v>
       </c>
       <c r="V45" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W45" t="n">
         <v>3.25</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -12033,160 +12033,160 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="G46" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H46" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I46" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="K46" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="L46" t="n">
         <v>1.4</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P46" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="T46" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="U46" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="V46" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="W46" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -12287,40 +12287,40 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="G47" t="n">
         <v>5.6</v>
       </c>
       <c r="H47" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K47" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L47" t="n">
         <v>1.47</v>
       </c>
       <c r="M47" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N47" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O47" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P47" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R47" t="n">
         <v>1.19</v>
@@ -12335,10 +12335,10 @@
         <v>1.72</v>
       </c>
       <c r="V47" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="W47" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X47" t="n">
         <v>970</v>
@@ -12365,7 +12365,7 @@
         <v>36</v>
       </c>
       <c r="AF47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG47" t="n">
         <v>24</v>
@@ -12380,7 +12380,7 @@
         <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
         <v>1000</v>
@@ -12395,58 +12395,58 @@
         <v>36</v>
       </c>
       <c r="AP47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS47" t="n">
         <v>3.1</v>
       </c>
-      <c r="AQ47" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AR47" t="n">
+      <c r="AT47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE47" t="n">
         <v>3.35</v>
       </c>
-      <c r="AS47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV47" t="n">
+      <c r="BF47" t="n">
         <v>3.3</v>
       </c>
-      <c r="AW47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG47" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12488,7 +12488,7 @@
         <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -12822,19 +12822,19 @@
         <v>1.26</v>
       </c>
       <c r="O49" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="P49" t="n">
         <v>1.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R49" t="n">
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T49" t="n">
         <v>1.11</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.22</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H50" t="n">
         <v>2.8</v>
@@ -13073,7 +13073,7 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="O50" t="n">
         <v>1.4</v>
@@ -13088,7 +13088,7 @@
         <v>1.19</v>
       </c>
       <c r="S50" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T50" t="n">
         <v>1.11</v>
@@ -13100,7 +13100,7 @@
         <v>1.32</v>
       </c>
       <c r="W50" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>2.44</v>
       </c>
       <c r="I51" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J51" t="n">
         <v>3.65</v>
@@ -13327,10 +13327,10 @@
         <v>1.06</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O51" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P51" t="n">
         <v>2.08</v>
@@ -13342,10 +13342,10 @@
         <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T51" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U51" t="n">
         <v>2.3</v>
@@ -13357,7 +13357,7 @@
         <v>1.48</v>
       </c>
       <c r="X51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y51" t="n">
         <v>14</v>
@@ -13381,7 +13381,7 @@
         <v>29</v>
       </c>
       <c r="AF51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG51" t="n">
         <v>15.5</v>
@@ -13420,7 +13420,7 @@
         <v>12.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT51" t="n">
         <v>10.5</v>
@@ -13444,19 +13444,19 @@
         <v>14.5</v>
       </c>
       <c r="BA51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC51" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BD51" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC51" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE51" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF51" t="n">
         <v>21</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -13563,16 +13563,16 @@
         <v>1.83</v>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J52" t="n">
         <v>4.8</v>
       </c>
       <c r="K52" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13590,7 +13590,7 @@
         <v>2.96</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="R52" t="n">
         <v>1.76</v>
@@ -13599,7 +13599,7 @@
         <v>1.8</v>
       </c>
       <c r="T52" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U52" t="n">
         <v>2.92</v>
@@ -13614,7 +13614,7 @@
         <v>55</v>
       </c>
       <c r="Y52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z52" t="n">
         <v>55</v>
@@ -13623,7 +13623,7 @@
         <v>95</v>
       </c>
       <c r="AB52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC52" t="n">
         <v>16.5</v>
@@ -13638,7 +13638,7 @@
         <v>21</v>
       </c>
       <c r="AG52" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH52" t="n">
         <v>19.5</v>
@@ -13647,19 +13647,19 @@
         <v>44</v>
       </c>
       <c r="AJ52" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK52" t="n">
         <v>19</v>
       </c>
       <c r="AL52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM52" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN52" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO52" t="n">
         <v>26</v>
@@ -13689,7 +13689,7 @@
         <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY52" t="n">
         <v>8.4</v>
@@ -13713,10 +13713,10 @@
         <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG52" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -13814,19 +13814,19 @@
         <v>2.64</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H53" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I53" t="n">
         <v>2.62</v>
       </c>
       <c r="J53" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K53" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13835,7 +13835,7 @@
         <v>1.03</v>
       </c>
       <c r="N53" t="n">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.14</v>
@@ -13844,16 +13844,16 @@
         <v>2.48</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S53" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="T53" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U53" t="n">
         <v>2.74</v>
@@ -13862,13 +13862,13 @@
         <v>1.61</v>
       </c>
       <c r="W53" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y53" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z53" t="n">
         <v>24</v>
@@ -13877,7 +13877,7 @@
         <v>40</v>
       </c>
       <c r="AB53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="n">
         <v>12</v>
@@ -13919,19 +13919,19 @@
         <v>14</v>
       </c>
       <c r="AP53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ53" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT53" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU53" t="n">
         <v>8</v>
@@ -13943,7 +13943,7 @@
         <v>17.5</v>
       </c>
       <c r="AX53" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY53" t="n">
         <v>10</v>
@@ -13955,22 +13955,22 @@
         <v>21</v>
       </c>
       <c r="BB53" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC53" t="n">
         <v>19.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE53" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF53" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -14065,46 +14065,46 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="G54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K54" t="n">
         <v>3.6</v>
       </c>
-      <c r="H54" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K54" t="n">
-        <v>8.6</v>
-      </c>
       <c r="L54" t="n">
         <v>1.01</v>
       </c>
       <c r="M54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N54" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="O54" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="P54" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="R54" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S54" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="T54" t="n">
         <v>1.93</v>
@@ -14113,10 +14113,10 @@
         <v>1.67</v>
       </c>
       <c r="V54" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W54" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X54" t="n">
         <v>970</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -15628,7 +15628,7 @@
         <v>1.12</v>
       </c>
       <c r="S60" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T60" t="n">
         <v>1.01</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
         <v>1.3</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H61" t="n">
         <v>1.14</v>
@@ -15855,7 +15855,7 @@
         <v>1000</v>
       </c>
       <c r="J61" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K61" t="n">
         <v>1000</v>
@@ -15867,7 +15867,7 @@
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O61" t="n">
         <v>1.09</v>
@@ -15876,7 +15876,7 @@
         <v>1.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R61" t="n">
         <v>1.18</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -16124,16 +16124,16 @@
         <v>2.62</v>
       </c>
       <c r="O62" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P62" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q62" t="n">
         <v>2.58</v>
       </c>
       <c r="R62" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S62" t="n">
         <v>5.3</v>
@@ -16154,7 +16154,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z62" t="n">
         <v>25</v>
@@ -16193,7 +16193,7 @@
         <v>44</v>
       </c>
       <c r="AL62" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM62" t="n">
         <v>210</v>
@@ -16202,10 +16202,10 @@
         <v>50</v>
       </c>
       <c r="AO62" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP62" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ62" t="n">
         <v>8.199999999999999</v>
@@ -16214,7 +16214,7 @@
         <v>18</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT62" t="n">
         <v>6.8</v>
@@ -16226,7 +16226,7 @@
         <v>12.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX62" t="n">
         <v>13</v>
@@ -16238,25 +16238,25 @@
         <v>19</v>
       </c>
       <c r="BA62" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC62" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB62" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD62" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF62" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -16351,19 +16351,19 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G63" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I63" t="n">
         <v>4.5</v>
       </c>
       <c r="J63" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K63" t="n">
         <v>3.1</v>
@@ -16375,16 +16375,16 @@
         <v>1.14</v>
       </c>
       <c r="N63" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O63" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P63" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R63" t="n">
         <v>1.17</v>
@@ -16393,16 +16393,16 @@
         <v>6.2</v>
       </c>
       <c r="T63" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U63" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V63" t="n">
         <v>1.29</v>
       </c>
       <c r="W63" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X63" t="n">
         <v>8.6</v>
@@ -16414,7 +16414,7 @@
         <v>29</v>
       </c>
       <c r="AA63" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB63" t="n">
         <v>6.8</v>
@@ -16423,7 +16423,7 @@
         <v>7.6</v>
       </c>
       <c r="AD63" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE63" t="n">
         <v>85</v>
@@ -16432,10 +16432,10 @@
         <v>13.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH63" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI63" t="n">
         <v>130</v>
@@ -16444,19 +16444,19 @@
         <v>38</v>
       </c>
       <c r="AK63" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL63" t="n">
         <v>80</v>
       </c>
       <c r="AM63" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN63" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO63" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP63" t="n">
         <v>6.6</v>
@@ -16465,10 +16465,10 @@
         <v>8.4</v>
       </c>
       <c r="AR63" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS63" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT63" t="n">
         <v>5.7</v>
@@ -16477,10 +16477,10 @@
         <v>6.2</v>
       </c>
       <c r="AV63" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW63" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX63" t="n">
         <v>10.5</v>
@@ -16489,28 +16489,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ63" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA63" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB63" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC63" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD63" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF63" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE63" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>7</v>
-      </c>
       <c r="BG63" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -16608,16 +16608,16 @@
         <v>1.97</v>
       </c>
       <c r="G64" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H64" t="n">
         <v>4.2</v>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K64" t="n">
         <v>3.65</v>
@@ -16629,31 +16629,31 @@
         <v>1.09</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O64" t="n">
         <v>1.41</v>
       </c>
       <c r="P64" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q64" t="n">
         <v>2.14</v>
       </c>
       <c r="R64" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S64" t="n">
         <v>4.2</v>
       </c>
       <c r="T64" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U64" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V64" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W64" t="n">
         <v>1.86</v>
@@ -16662,25 +16662,25 @@
         <v>13.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z64" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA64" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB64" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC64" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD64" t="n">
         <v>22</v>
       </c>
       <c r="AE64" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF64" t="n">
         <v>12.5</v>
@@ -16689,10 +16689,10 @@
         <v>12.5</v>
       </c>
       <c r="AH64" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI64" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ64" t="n">
         <v>25</v>
@@ -16710,49 +16710,49 @@
         <v>970</v>
       </c>
       <c r="AO64" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP64" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ64" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS64" t="n">
         <v>1.01</v>
       </c>
       <c r="AT64" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU64" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU64" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV64" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AW64" t="n">
         <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ64" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA64" t="n">
         <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD64" t="n">
         <v>1.01</v>
@@ -16761,28 +16761,28 @@
         <v>1.01</v>
       </c>
       <c r="BF64" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG64" t="n">
         <v>1.01</v>
       </c>
       <c r="BH64" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.61</v>
+        <v>2.36</v>
       </c>
       <c r="BN64" t="n">
         <v>4.6</v>
@@ -16794,13 +16794,13 @@
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT64" t="n">
         <v>8</v>
@@ -16812,23 +16812,23 @@
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="BZ64" t="n">
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -16859,64 +16859,64 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G65" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H65" t="n">
         <v>2.18</v>
       </c>
       <c r="I65" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J65" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K65" t="n">
         <v>3.55</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M65" t="n">
         <v>1.09</v>
       </c>
       <c r="N65" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O65" t="n">
         <v>1.41</v>
       </c>
       <c r="P65" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R65" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T65" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U65" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V65" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W65" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X65" t="n">
         <v>13</v>
       </c>
       <c r="Y65" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z65" t="n">
         <v>15.5</v>
@@ -16940,7 +16940,7 @@
         <v>32</v>
       </c>
       <c r="AG65" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH65" t="n">
         <v>23</v>
@@ -16967,22 +16967,22 @@
         <v>27</v>
       </c>
       <c r="AP65" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ65" t="n">
         <v>7.2</v>
       </c>
       <c r="AR65" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT65" t="n">
         <v>9.4</v>
       </c>
       <c r="AU65" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV65" t="n">
         <v>9.6</v>
@@ -16994,95 +16994,95 @@
         <v>20</v>
       </c>
       <c r="AY65" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ65" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA65" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB65" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC65" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD65" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE65" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF65" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG65" t="n">
         <v>18</v>
       </c>
       <c r="BH65" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="BI65" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK65" t="n">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>1.37</v>
+        <v>10</v>
       </c>
       <c r="BN65" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO65" t="n">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="BP65" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ65" t="n">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR65" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS65" t="n">
-        <v>1.37</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT65" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU65" t="n">
-        <v>1.37</v>
+        <v>3.95</v>
       </c>
       <c r="BV65" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW65" t="n">
-        <v>1.37</v>
+        <v>6.6</v>
       </c>
       <c r="BX65" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY65" t="n">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ65" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -17113,13 +17113,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G66" t="n">
         <v>2.38</v>
       </c>
       <c r="H66" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I66" t="n">
         <v>3.75</v>
@@ -17128,7 +17128,7 @@
         <v>3.3</v>
       </c>
       <c r="K66" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -17143,25 +17143,25 @@
         <v>1.3</v>
       </c>
       <c r="P66" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R66" t="n">
         <v>1.38</v>
       </c>
       <c r="S66" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T66" t="n">
         <v>1.72</v>
       </c>
       <c r="U66" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V66" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W66" t="n">
         <v>1.72</v>
@@ -17173,7 +17173,7 @@
         <v>14.5</v>
       </c>
       <c r="Z66" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA66" t="n">
         <v>65</v>
@@ -17200,13 +17200,13 @@
         <v>16.5</v>
       </c>
       <c r="AI66" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ66" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL66" t="n">
         <v>38</v>
@@ -17215,7 +17215,7 @@
         <v>95</v>
       </c>
       <c r="AN66" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AO66" t="n">
         <v>40</v>
@@ -17269,7 +17269,7 @@
         <v>13.5</v>
       </c>
       <c r="BF66" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG66" t="n">
         <v>27</v>
@@ -17299,25 +17299,25 @@
         <v>4.6</v>
       </c>
       <c r="BP66" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ66" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR66" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS66" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT66" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU66" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV66" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BW66" t="n">
         <v>10</v>
@@ -17329,14 +17329,14 @@
         <v>11</v>
       </c>
       <c r="BZ66" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA66" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
         <v>4.3</v>
       </c>
       <c r="H67" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I67" t="n">
         <v>2.46</v>
@@ -17394,7 +17394,7 @@
         <v>2.44</v>
       </c>
       <c r="O67" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P67" t="n">
         <v>1.62</v>
@@ -17457,7 +17457,7 @@
         <v>60</v>
       </c>
       <c r="AJ67" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK67" t="n">
         <v>65</v>
@@ -17469,13 +17469,13 @@
         <v>170</v>
       </c>
       <c r="AN67" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO67" t="n">
         <v>34</v>
       </c>
       <c r="AP67" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ67" t="n">
         <v>6.2</v>
@@ -17484,10 +17484,10 @@
         <v>10.5</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT67" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU67" t="n">
         <v>5.7</v>
@@ -17499,7 +17499,7 @@
         <v>1.01</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY67" t="n">
         <v>12.5</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
         <v>2.46</v>
       </c>
       <c r="O68" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="P68" t="n">
         <v>1.5</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
         <v>4.8</v>
       </c>
       <c r="L69" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M69" t="n">
         <v>1.05</v>
@@ -17917,7 +17917,7 @@
         <v>2.8</v>
       </c>
       <c r="T69" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U69" t="n">
         <v>2.08</v>
@@ -17935,7 +17935,7 @@
         <v>27</v>
       </c>
       <c r="Z69" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA69" t="n">
         <v>190</v>
@@ -17992,7 +17992,7 @@
         <v>5.5</v>
       </c>
       <c r="AS69" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT69" t="n">
         <v>8.6</v>
@@ -18004,7 +18004,7 @@
         <v>21</v>
       </c>
       <c r="AW69" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX69" t="n">
         <v>9.199999999999999</v>
@@ -18016,7 +18016,7 @@
         <v>18</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB69" t="n">
         <v>13</v>
@@ -18028,7 +18028,7 @@
         <v>5.3</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF69" t="n">
         <v>6</v>
@@ -18037,68 +18037,68 @@
         <v>5.8</v>
       </c>
       <c r="BH69" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI69" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK69" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
       </c>
       <c r="BM69" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN69" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO69" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP69" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ69" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR69" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS69" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT69" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU69" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV69" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW69" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX69" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY69" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ69" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -18135,13 +18135,13 @@
         <v>1.54</v>
       </c>
       <c r="H70" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="I70" t="n">
         <v>1000</v>
       </c>
       <c r="J70" t="n">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="K70" t="n">
         <v>1000</v>
@@ -18153,7 +18153,7 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O70" t="n">
         <v>1.1</v>
@@ -18180,7 +18180,7 @@
         <v>1.1</v>
       </c>
       <c r="W70" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G71" t="n">
         <v>2.32</v>
@@ -18461,7 +18461,7 @@
         <v>55</v>
       </c>
       <c r="AF71" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG71" t="n">
         <v>12</v>
@@ -18497,10 +18497,10 @@
         <v>10.5</v>
       </c>
       <c r="AR71" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AS71" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT71" t="n">
         <v>7.2</v>
@@ -18512,7 +18512,7 @@
         <v>13.5</v>
       </c>
       <c r="AW71" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX71" t="n">
         <v>11.5</v>
@@ -18524,25 +18524,25 @@
         <v>16.5</v>
       </c>
       <c r="BA71" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB71" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC71" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BC71" t="n">
-        <v>6.4</v>
       </c>
       <c r="BD71" t="n">
         <v>7.2</v>
       </c>
       <c r="BE71" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF71" t="n">
         <v>17</v>
       </c>
       <c r="BG71" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH71" t="n">
         <v>1000</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -19408,13 +19408,13 @@
         <v>4.3</v>
       </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K75" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L75" t="n">
         <v>1.56</v>
@@ -19447,10 +19447,10 @@
         <v>1.49</v>
       </c>
       <c r="V75" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W75" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X75" t="n">
         <v>8.6</v>
@@ -19465,7 +19465,7 @@
         <v>180</v>
       </c>
       <c r="AB75" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC75" t="n">
         <v>9</v>
@@ -19480,7 +19480,7 @@
         <v>13.5</v>
       </c>
       <c r="AG75" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH75" t="n">
         <v>38</v>
@@ -19492,7 +19492,7 @@
         <v>36</v>
       </c>
       <c r="AK75" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL75" t="n">
         <v>100</v>
@@ -19501,19 +19501,19 @@
         <v>390</v>
       </c>
       <c r="AN75" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO75" t="n">
         <v>250</v>
       </c>
       <c r="AP75" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS75" t="n">
         <v>1.01</v>
@@ -19522,7 +19522,7 @@
         <v>4.6</v>
       </c>
       <c r="AU75" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV75" t="n">
         <v>16</v>
@@ -19543,7 +19543,7 @@
         <v>1.01</v>
       </c>
       <c r="BB75" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC75" t="n">
         <v>1.03</v>
@@ -19585,7 +19585,7 @@
         <v>3.5</v>
       </c>
       <c r="BP75" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ75" t="n">
         <v>7</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -857,145 +857,145 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.49</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
@@ -1019,13 +1019,13 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
@@ -1037,7 +1037,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
@@ -1055,13 +1055,13 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU2" t="n">
         <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
         <v>2.84</v>
@@ -1443,28 +1443,28 @@
         <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
         <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
         <v>30</v>
@@ -1473,58 +1473,58 @@
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="I5" t="n">
-        <v>2.64</v>
+        <v>2.14</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1652,13 +1652,13 @@
         <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
@@ -1915,16 +1915,16 @@
         <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2127,34 +2127,34 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.12</v>
@@ -2163,34 +2163,34 @@
         <v>1.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
         <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2199,10 +2199,10 @@
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -2211,19 +2211,19 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -2232,91 +2232,91 @@
         <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BH7" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2328,29 +2328,29 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
         <v>2.04</v>
       </c>
       <c r="I10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,16 +2913,16 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
@@ -2937,7 +2937,7 @@
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W10" t="n">
         <v>1.35</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3693,16 +3693,16 @@
         <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -3905,70 +3905,70 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W14" t="n">
         <v>2.12</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.24</v>
       </c>
       <c r="X14" t="n">
         <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
@@ -3977,10 +3977,10 @@
         <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
         <v>14</v>
@@ -4019,10 +4019,10 @@
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
@@ -4034,7 +4034,7 @@
         <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
         <v>8.4</v>
@@ -4046,7 +4046,7 @@
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
         <v>13.5</v>
@@ -4055,22 +4055,22 @@
         <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.800000000000001</v>
@@ -4085,13 +4085,13 @@
         <v>13</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>8.800000000000001</v>
@@ -4100,10 +4100,10 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BU14" t="n">
         <v>6.6</v>
@@ -4112,7 +4112,7 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.34</v>
@@ -4192,7 +4192,7 @@
         <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
@@ -4201,10 +4201,10 @@
         <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.54</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.37</v>
@@ -4715,10 +4715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
         <v>1.02</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q18" t="n">
         <v>1.46</v>
@@ -4960,7 +4960,7 @@
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.26</v>
@@ -5199,88 +5199,88 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.3</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.34</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="X19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA19" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
         <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AP19" t="n">
         <v>4.3</v>
@@ -5295,55 +5295,55 @@
         <v>4.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW19" t="n">
         <v>4.5</v>
       </c>
       <c r="AX19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC19" t="n">
+      <c r="BD19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG19" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19" t="n">
         <v>5.3</v>
@@ -5352,53 +5352,53 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW19" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BX19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BY19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5471,10 @@
         <v>2.08</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
         <v>3.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ22" t="n">
         <v>10</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.02</v>
+        <v>1.09</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.98</v>
+        <v>3.7</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6242,7 +6242,7 @@
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -6487,10 +6487,10 @@
         <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
         <v>1.25</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="G26" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.37</v>
@@ -6995,13 +6995,13 @@
         <v>3.45</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
         <v>1.61</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.12</v>
@@ -7246,7 +7246,7 @@
         <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
@@ -7485,7 +7485,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.33</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>1.22</v>
@@ -7500,7 +7500,7 @@
         <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
@@ -7739,13 +7739,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O29" t="n">
         <v>1.12</v>
       </c>
       <c r="P29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q29" t="n">
         <v>1.12</v>
@@ -7757,10 +7757,10 @@
         <v>1.12</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G31" t="n">
         <v>6.2</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -8480,13 +8480,13 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H32" t="n">
         <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>4.2</v>
@@ -8516,7 +8516,7 @@
         <v>1.88</v>
       </c>
       <c r="S32" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="T32" t="n">
         <v>1.42</v>
@@ -8525,10 +8525,10 @@
         <v>2.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X32" t="n">
         <v>48</v>
@@ -8633,7 +8633,7 @@
         <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG32" t="n">
         <v>11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H33" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>4.2</v>
@@ -8758,7 +8758,7 @@
         <v>4.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P33" t="n">
         <v>2.16</v>
@@ -8770,7 +8770,7 @@
         <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T33" t="n">
         <v>1.59</v>
@@ -8779,13 +8779,13 @@
         <v>2.32</v>
       </c>
       <c r="V33" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W33" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y33" t="n">
         <v>15.5</v>
@@ -8794,7 +8794,7 @@
         <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB33" t="n">
         <v>17</v>
@@ -8809,10 +8809,10 @@
         <v>29</v>
       </c>
       <c r="AF33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
         <v>18</v>
@@ -8821,7 +8821,7 @@
         <v>38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK33" t="n">
         <v>34</v>
@@ -8833,10 +8833,10 @@
         <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO33" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AP33" t="n">
         <v>14.5</v>
@@ -8845,10 +8845,10 @@
         <v>10</v>
       </c>
       <c r="AR33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT33" t="n">
         <v>11</v>
@@ -8857,13 +8857,13 @@
         <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW33" t="n">
         <v>19</v>
       </c>
       <c r="AX33" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
@@ -8872,25 +8872,25 @@
         <v>12</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH33" t="n">
         <v>4.1</v>
@@ -8902,16 +8902,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO33" t="n">
         <v>4.9</v>
@@ -8920,7 +8920,7 @@
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
@@ -8929,7 +8929,7 @@
         <v>7.6</v>
       </c>
       <c r="BT33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU33" t="n">
         <v>4.5</v>
@@ -8938,13 +8938,13 @@
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -9012,13 +9012,13 @@
         <v>1.01</v>
       </c>
       <c r="O34" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P34" t="n">
         <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R34" t="n">
         <v>1.8</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G35" t="n">
         <v>2.04</v>
@@ -9272,13 +9272,13 @@
         <v>3.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="R35" t="n">
         <v>2.02</v>
       </c>
       <c r="S35" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="T35" t="n">
         <v>1.34</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T36" t="n">
         <v>1.74</v>
@@ -9658,7 +9658,7 @@
         <v>6.4</v>
       </c>
       <c r="BI36" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G37" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H37" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="I37" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.21</v>
@@ -9777,7 +9777,7 @@
         <v>1.16</v>
       </c>
       <c r="P37" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q37" t="n">
         <v>1.49</v>
@@ -9792,13 +9792,13 @@
         <v>1.58</v>
       </c>
       <c r="U37" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V37" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X37" t="n">
         <v>36</v>
@@ -9810,7 +9810,7 @@
         <v>16</v>
       </c>
       <c r="AA37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB37" t="n">
         <v>32</v>
@@ -9822,7 +9822,7 @@
         <v>11</v>
       </c>
       <c r="AE37" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF37" t="n">
         <v>55</v>
@@ -9852,7 +9852,7 @@
         <v>48</v>
       </c>
       <c r="AO37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP37" t="n">
         <v>21</v>
@@ -9903,7 +9903,7 @@
         <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BG37" t="n">
         <v>4.8</v>
@@ -9915,34 +9915,34 @@
         <v>3.7</v>
       </c>
       <c r="BJ37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO37" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ37" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS37" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT37" t="n">
         <v>4.9</v>
@@ -9954,13 +9954,13 @@
         <v>10.5</v>
       </c>
       <c r="BW37" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BX37" t="n">
         <v>19.5</v>
       </c>
       <c r="BY37" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -10001,25 +10001,25 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="G38" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K38" t="n">
         <v>4.6</v>
       </c>
       <c r="L38" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M38" t="n">
         <v>1.04</v>
@@ -10031,10 +10031,10 @@
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="R38" t="n">
         <v>1.53</v>
@@ -10046,25 +10046,25 @@
         <v>1.6</v>
       </c>
       <c r="U38" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V38" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="X38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA38" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="n">
         <v>14.5</v>
@@ -10073,13 +10073,13 @@
         <v>11.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG38" t="n">
         <v>12.5</v>
@@ -10088,31 +10088,31 @@
         <v>19</v>
       </c>
       <c r="AI38" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL38" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM38" t="n">
         <v>80</v>
       </c>
       <c r="AN38" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP38" t="n">
         <v>17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR38" t="n">
         <v>1.03</v>
@@ -10121,22 +10121,22 @@
         <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU38" t="n">
         <v>7.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW38" t="n">
         <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ38" t="n">
         <v>12.5</v>
@@ -10145,10 +10145,10 @@
         <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD38" t="n">
         <v>21</v>
@@ -10157,7 +10157,7 @@
         <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG38" t="n">
         <v>1.01</v>
@@ -10169,62 +10169,62 @@
         <v>3.4</v>
       </c>
       <c r="BJ38" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ38" t="n">
         <v>5.6</v>
       </c>
       <c r="BR38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS38" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT38" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU38" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY38" t="n">
         <v>7.6</v>
       </c>
-      <c r="BX38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY38" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA38" t="n">
         <v>6.2</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O39" t="n">
         <v>1.27</v>
@@ -10294,7 +10294,7 @@
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>2.74</v>
+        <v>1.27</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -10509,19 +10509,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H40" t="n">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.1</v>
+        <v>1.96</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>1.88</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
         <v>18.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT41" t="n">
         <v>5.7</v>
@@ -10892,37 +10892,37 @@
         <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX41" t="n">
         <v>11</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH41" t="n">
         <v>2.68</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H42" t="n">
         <v>3.15</v>
       </c>
       <c r="I42" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>2.98</v>
@@ -11038,34 +11038,34 @@
         <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O42" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P42" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
         <v>1.87</v>
       </c>
       <c r="U42" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="V42" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W42" t="n">
         <v>1.58</v>
@@ -11092,7 +11092,7 @@
         <v>970</v>
       </c>
       <c r="AE42" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF42" t="n">
         <v>970</v>
@@ -11107,10 +11107,10 @@
         <v>65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK42" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL42" t="n">
         <v>60</v>
@@ -11125,16 +11125,16 @@
         <v>55</v>
       </c>
       <c r="AP42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ42" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AR42" t="n">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="AS42" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AT42" t="n">
         <v>8</v>
@@ -11146,7 +11146,7 @@
         <v>11</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX42" t="n">
         <v>13.5</v>
@@ -11155,28 +11155,28 @@
         <v>10</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BC42" t="n">
         <v>5.4</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH42" t="n">
         <v>3</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
         <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J43" t="n">
         <v>3.75</v>
@@ -11292,7 +11292,7 @@
         <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
         <v>3</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
         <v>3.05</v>
       </c>
       <c r="I44" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>3.75</v>
@@ -11543,7 +11543,7 @@
         <v>4.1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
@@ -11708,7 +11708,7 @@
         <v>5.7</v>
       </c>
       <c r="BO44" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP44" t="n">
         <v>16.5</v>
@@ -11726,7 +11726,7 @@
         <v>7</v>
       </c>
       <c r="BU44" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV44" t="n">
         <v>24</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
         <v>1.44</v>
       </c>
       <c r="H45" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I45" t="n">
         <v>14.5</v>
@@ -11800,7 +11800,7 @@
         <v>1.4</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N45" t="n">
         <v>2.78</v>
@@ -11845,7 +11845,7 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AC45" t="n">
         <v>13</v>
@@ -11887,58 +11887,58 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ45" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AR45" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS45" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT45" t="n">
         <v>3.15</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AV45" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ45" t="n">
         <v>6</v>
       </c>
-      <c r="AX45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BA45" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE45" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF45" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BG45" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -12287,37 +12287,37 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="G47" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H47" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="J47" t="n">
         <v>2.72</v>
       </c>
       <c r="K47" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L47" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M47" t="n">
         <v>1.12</v>
       </c>
       <c r="N47" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O47" t="n">
         <v>1.52</v>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q47" t="n">
         <v>2.52</v>
@@ -12326,19 +12326,19 @@
         <v>1.19</v>
       </c>
       <c r="S47" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="T47" t="n">
         <v>2.1</v>
       </c>
       <c r="U47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V47" t="n">
         <v>1.72</v>
       </c>
-      <c r="V47" t="n">
-        <v>1.76</v>
-      </c>
       <c r="W47" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X47" t="n">
         <v>970</v>
@@ -12356,7 +12356,7 @@
         <v>970</v>
       </c>
       <c r="AC47" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD47" t="n">
         <v>970</v>
@@ -12365,13 +12365,13 @@
         <v>36</v>
       </c>
       <c r="AF47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH47" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI47" t="n">
         <v>75</v>
@@ -12380,7 +12380,7 @@
         <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL47" t="n">
         <v>1000</v>
@@ -12395,58 +12395,58 @@
         <v>36</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AQ47" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="AR47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT47" t="n">
         <v>3.5</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AU47" t="n">
         <v>3.1</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AV47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE47" t="n">
         <v>3.4</v>
       </c>
-      <c r="AU47" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BF47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BG47" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12488,7 +12488,7 @@
         <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -12583,10 +12583,10 @@
         <v>1.36</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V48" t="n">
         <v>1.02</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G49" t="n">
         <v>2.7</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
         <v>2.72</v>
       </c>
       <c r="H50" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
         <v>4.1</v>
@@ -13064,7 +13064,7 @@
         <v>2.78</v>
       </c>
       <c r="K50" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L50" t="n">
         <v>1.36</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
         <v>15.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD51" t="n">
         <v>13.5</v>
@@ -13420,7 +13420,7 @@
         <v>12.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT51" t="n">
         <v>10.5</v>
@@ -13444,19 +13444,19 @@
         <v>14.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF51" t="n">
         <v>21</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
         <v>4.8</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13641,7 +13641,7 @@
         <v>13.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI52" t="n">
         <v>44</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -13844,10 +13844,10 @@
         <v>2.48</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R53" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S53" t="n">
         <v>2.12</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -14869,10 +14869,10 @@
         <v>1.54</v>
       </c>
       <c r="T57" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V57" t="n">
         <v>1.01</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -15846,16 +15846,16 @@
         <v>1.3</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="H61" t="n">
-        <v>1.14</v>
+        <v>4.1</v>
       </c>
       <c r="I61" t="n">
         <v>1000</v>
       </c>
       <c r="J61" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="K61" t="n">
         <v>1000</v>
@@ -15894,7 +15894,7 @@
         <v>1.06</v>
       </c>
       <c r="W61" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -16100,13 +16100,13 @@
         <v>2.54</v>
       </c>
       <c r="G62" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H62" t="n">
         <v>3.15</v>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J62" t="n">
         <v>3.1</v>
@@ -16115,7 +16115,7 @@
         <v>3.25</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M62" t="n">
         <v>1.12</v>
@@ -16127,7 +16127,7 @@
         <v>1.52</v>
       </c>
       <c r="P62" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q62" t="n">
         <v>2.58</v>
@@ -16145,7 +16145,7 @@
         <v>1.79</v>
       </c>
       <c r="V62" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W62" t="n">
         <v>1.58</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16366,7 @@
         <v>2.98</v>
       </c>
       <c r="K63" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -16441,7 +16441,7 @@
         <v>130</v>
       </c>
       <c r="AJ63" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK63" t="n">
         <v>38</v>
@@ -16462,10 +16462,10 @@
         <v>6.6</v>
       </c>
       <c r="AQ63" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR63" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AS63" t="n">
         <v>8.4</v>
@@ -16477,10 +16477,10 @@
         <v>6.2</v>
       </c>
       <c r="AV63" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW63" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX63" t="n">
         <v>10.5</v>
@@ -16501,16 +16501,16 @@
         <v>7.2</v>
       </c>
       <c r="BD63" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE63" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF63" t="n">
         <v>7.4</v>
       </c>
       <c r="BG63" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G64" t="n">
         <v>2.16</v>
@@ -16644,7 +16644,7 @@
         <v>1.27</v>
       </c>
       <c r="S64" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T64" t="n">
         <v>1.84</v>
@@ -16716,13 +16716,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT64" t="n">
         <v>6</v>
@@ -16734,10 +16734,10 @@
         <v>13</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY64" t="n">
         <v>8.199999999999999</v>
@@ -16746,25 +16746,25 @@
         <v>15</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC64" t="n">
         <v>17.5</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH64" t="n">
         <v>3.15</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
         <v>1.41</v>
       </c>
       <c r="P65" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q65" t="n">
         <v>2.18</v>
@@ -16967,7 +16967,7 @@
         <v>27</v>
       </c>
       <c r="AP65" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ65" t="n">
         <v>7.2</v>
@@ -16982,7 +16982,7 @@
         <v>9.4</v>
       </c>
       <c r="AU65" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV65" t="n">
         <v>9.6</v>
@@ -16994,10 +16994,10 @@
         <v>20</v>
       </c>
       <c r="AY65" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AZ65" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA65" t="n">
         <v>5.1</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -17113,19 +17113,19 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G66" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H66" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I66" t="n">
         <v>3.75</v>
       </c>
       <c r="J66" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K66" t="n">
         <v>3.4</v>
@@ -17137,34 +17137,34 @@
         <v>1.07</v>
       </c>
       <c r="N66" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O66" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P66" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R66" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S66" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T66" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U66" t="n">
         <v>2.24</v>
       </c>
       <c r="V66" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W66" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X66" t="n">
         <v>14.5</v>
@@ -17233,7 +17233,7 @@
         <v>55</v>
       </c>
       <c r="AT66" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU66" t="n">
         <v>7</v>
@@ -17251,7 +17251,7 @@
         <v>10</v>
       </c>
       <c r="AZ66" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA66" t="n">
         <v>42</v>
@@ -17266,13 +17266,13 @@
         <v>32</v>
       </c>
       <c r="BE66" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF66" t="n">
         <v>15</v>
       </c>
       <c r="BG66" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BH66" t="n">
         <v>3.5</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -17367,19 +17367,19 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G67" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H67" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="I67" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K67" t="n">
         <v>3.4</v>
@@ -17394,7 +17394,7 @@
         <v>2.44</v>
       </c>
       <c r="O67" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P67" t="n">
         <v>1.62</v>
@@ -17415,10 +17415,10 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W67" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X67" t="n">
         <v>11.5</v>
@@ -17433,7 +17433,7 @@
         <v>40</v>
       </c>
       <c r="AB67" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC67" t="n">
         <v>8.4</v>
@@ -17445,10 +17445,10 @@
         <v>36</v>
       </c>
       <c r="AF67" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG67" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH67" t="n">
         <v>24</v>
@@ -17457,10 +17457,10 @@
         <v>60</v>
       </c>
       <c r="AJ67" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK67" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL67" t="n">
         <v>85</v>
@@ -17469,34 +17469,34 @@
         <v>170</v>
       </c>
       <c r="AN67" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO67" t="n">
         <v>34</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ67" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR67" t="n">
         <v>10.5</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT67" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU67" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AV67" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX67" t="n">
         <v>19.5</v>
@@ -17508,25 +17508,25 @@
         <v>15.5</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH67" t="n">
         <v>1000</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -17914,13 +17914,13 @@
         <v>1.48</v>
       </c>
       <c r="S69" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T69" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U69" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V69" t="n">
         <v>1.17</v>
@@ -17929,13 +17929,13 @@
         <v>2.6</v>
       </c>
       <c r="X69" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="n">
         <v>27</v>
       </c>
       <c r="Z69" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA69" t="n">
         <v>190</v>
@@ -17989,13 +17989,13 @@
         <v>20</v>
       </c>
       <c r="AR69" t="n">
-        <v>5.5</v>
+        <v>28</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT69" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU69" t="n">
         <v>9.199999999999999</v>
@@ -18004,19 +18004,19 @@
         <v>21</v>
       </c>
       <c r="AW69" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AX69" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY69" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ69" t="n">
         <v>18</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="BB69" t="n">
         <v>13</v>
@@ -18025,16 +18025,16 @@
         <v>14</v>
       </c>
       <c r="BD69" t="n">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF69" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG69" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BH69" t="n">
         <v>3.95</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -18135,7 +18135,7 @@
         <v>1.54</v>
       </c>
       <c r="H70" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="I70" t="n">
         <v>1000</v>
@@ -18153,13 +18153,13 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.26</v>
+        <v>1.98</v>
       </c>
       <c r="O70" t="n">
         <v>1.1</v>
       </c>
       <c r="P70" t="n">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q70" t="n">
         <v>1.1</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -18676,7 +18676,7 @@
         <v>1.18</v>
       </c>
       <c r="S72" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T72" t="n">
         <v>2.1</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -19399,16 +19399,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G75" t="n">
         <v>2.26</v>
       </c>
       <c r="H75" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J75" t="n">
         <v>3.05</v>
@@ -19447,22 +19447,22 @@
         <v>1.49</v>
       </c>
       <c r="V75" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W75" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X75" t="n">
         <v>8.6</v>
       </c>
       <c r="Y75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z75" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA75" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB75" t="n">
         <v>7</v>
@@ -19471,10 +19471,10 @@
         <v>9</v>
       </c>
       <c r="AD75" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE75" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF75" t="n">
         <v>13.5</v>
@@ -19486,7 +19486,7 @@
         <v>38</v>
       </c>
       <c r="AI75" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ75" t="n">
         <v>36</v>
@@ -19504,22 +19504,22 @@
         <v>44</v>
       </c>
       <c r="AO75" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP75" t="n">
         <v>5.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT75" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU75" t="n">
         <v>5.8</v>
@@ -19528,37 +19528,37 @@
         <v>16</v>
       </c>
       <c r="AW75" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX75" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY75" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ75" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA75" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF75" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG75" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH75" t="n">
         <v>2.54</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
         <v>3.45</v>
@@ -881,7 +881,7 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
         <v>1.51</v>
@@ -890,13 +890,13 @@
         <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>2.04</v>
@@ -905,10 +905,10 @@
         <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
         <v>10.5</v>
@@ -965,25 +965,25 @@
         <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AW2" t="n">
         <v>3.95</v>
@@ -992,7 +992,7 @@
         <v>3.85</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
         <v>3.8</v>
@@ -1016,7 +1016,7 @@
         <v>4.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="n">
         <v>2.84</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
         <v>1.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,7 +1135,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.06</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.23</v>
@@ -1147,10 +1147,10 @@
         <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,13 +1159,13 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1267,74 +1267,74 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
         <v>1.83</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
@@ -1398,28 +1398,28 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1476,7 +1476,7 @@
         <v>3.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AR4" t="n">
         <v>3.3</v>
@@ -1488,10 +1488,10 @@
         <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AW4" t="n">
         <v>3.5</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1643,10 +1643,10 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.32</v>
@@ -1655,7 +1655,7 @@
         <v>1.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
         <v>2.58</v>
@@ -1670,7 +1670,7 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X5" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G6" t="n">
         <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
@@ -1906,28 +1906,28 @@
         <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
         <v>13.5</v>
@@ -1957,7 +1957,7 @@
         <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
         <v>40</v>
@@ -1972,7 +1972,7 @@
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
         <v>40</v>
@@ -1981,7 +1981,7 @@
         <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>9.6</v>
@@ -1990,13 +1990,13 @@
         <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
         <v>9.6</v>
@@ -2011,28 +2011,28 @@
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2127,61 +2127,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="W7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2193,103 +2193,103 @@
         <v>28</v>
       </c>
       <c r="AB7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG7" t="n">
         <v>970</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>20</v>
       </c>
       <c r="AH7" t="n">
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL7" t="n">
         <v>50</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>80</v>
       </c>
       <c r="AN7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI7" t="n">
         <v>3.25</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
         <v>2.02</v>
@@ -2498,13 +2498,13 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2534,7 +2534,7 @@
         <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
@@ -2546,7 +2546,7 @@
         <v>3.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.75</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
         <v>7.4</v>
@@ -2650,31 +2650,31 @@
         <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
         <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.96</v>
@@ -2689,7 +2689,7 @@
         <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2746,49 +2746,49 @@
         <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2898,10 +2898,10 @@
         <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
         <v>4.6</v>
@@ -2937,7 +2937,7 @@
         <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
         <v>2.14</v>
@@ -3003,10 +3003,10 @@
         <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
         <v>9.4</v>
@@ -3030,7 +3030,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -3039,80 +3039,80 @@
         <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
         <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="I11" t="n">
         <v>1.55</v>
@@ -3158,7 +3158,7 @@
         <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.35</v>
@@ -3176,7 +3176,7 @@
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
         <v>1.42</v>
@@ -3185,7 +3185,7 @@
         <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
         <v>1.9</v>
@@ -3251,7 +3251,7 @@
         <v>7.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>7</v>
@@ -3275,7 +3275,7 @@
         <v>13.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>21</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>1.76</v>
       </c>
       <c r="G12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
         <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3445,10 +3445,10 @@
         <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -3511,10 +3511,10 @@
         <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3526,7 +3526,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX12" t="n">
         <v>8.6</v>
@@ -3538,7 +3538,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
         <v>14</v>
@@ -3547,16 +3547,16 @@
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="n">
         <v>3.75</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -3705,7 +3705,7 @@
         <v>1.96</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y13" t="n">
         <v>16</v>
@@ -3798,7 +3798,7 @@
         <v>17.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.8</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>5.3</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I14" t="n">
         <v>2.62</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.65</v>
@@ -3944,7 +3944,7 @@
         <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
@@ -3956,7 +3956,7 @@
         <v>1.61</v>
       </c>
       <c r="W14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
         <v>15</v>
@@ -4016,22 +4016,22 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>20</v>
@@ -4040,28 +4040,28 @@
         <v>16.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG14" t="n">
         <v>18</v>
@@ -4070,7 +4070,7 @@
         <v>3.25</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
@@ -4183,7 +4183,7 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
         <v>1.43</v>
@@ -4198,10 +4198,10 @@
         <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
         <v>1.73</v>
@@ -4324,7 +4324,7 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -4425,10 +4425,10 @@
         <v>4.9</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.5</v>
@@ -4437,7 +4437,7 @@
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
         <v>1.56</v>
@@ -4446,7 +4446,7 @@
         <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -4458,7 +4458,7 @@
         <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
         <v>1.27</v>
@@ -4470,7 +4470,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
         <v>36</v>
@@ -4521,7 +4521,7 @@
         <v>150</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AQ16" t="n">
         <v>3.3</v>
@@ -4533,7 +4533,7 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AU16" t="n">
         <v>2.92</v>
@@ -4578,7 +4578,7 @@
         <v>2.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4593,7 +4593,7 @@
         <v>1.47</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO16" t="n">
         <v>3.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>3.45</v>
@@ -4700,7 +4700,7 @@
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
@@ -4781,7 +4781,7 @@
         <v>3.45</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS17" t="n">
         <v>4.6</v>
@@ -4793,7 +4793,7 @@
         <v>3.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW17" t="n">
         <v>4.5</v>
@@ -4811,7 +4811,7 @@
         <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC17" t="n">
         <v>4.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="K19" t="n">
-        <v>410</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -5205,16 +5205,16 @@
         <v>1.43</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -5223,13 +5223,13 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -5340,65 +5340,65 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>9.6</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K20" t="n">
         <v>5.6</v>
@@ -5468,7 +5468,7 @@
         <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="T20" t="n">
         <v>1.72</v>
@@ -5480,7 +5480,7 @@
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5585,74 +5585,74 @@
         <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G21" t="n">
         <v>2.22</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
         <v>3.7</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G22" t="n">
         <v>1.87</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>4.8</v>
@@ -5952,7 +5952,7 @@
         <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5997,13 +5997,13 @@
         <v>32</v>
       </c>
       <c r="Z22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC22" t="n">
         <v>14</v>
@@ -6045,16 +6045,16 @@
         <v>32</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT22" t="n">
         <v>12</v>
@@ -6066,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX22" t="n">
         <v>11.5</v>
@@ -6078,7 +6078,7 @@
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
         <v>15.5</v>
@@ -6090,77 +6090,77 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>3.15</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
         <v>4.1</v>
@@ -6269,7 +6269,7 @@
         <v>34</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
         <v>13.5</v>
@@ -6284,7 +6284,7 @@
         <v>36</v>
       </c>
       <c r="AK23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL23" t="n">
         <v>36</v>
@@ -6299,52 +6299,52 @@
         <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>18.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY23" t="n">
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BC23" t="n">
         <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF23" t="n">
         <v>12</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.35</v>
@@ -6475,10 +6475,10 @@
         <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
         <v>1.41</v>
@@ -6490,16 +6490,16 @@
         <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
         <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
         <v>19</v>
@@ -6514,7 +6514,7 @@
         <v>10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>19.5</v>
@@ -6523,19 +6523,19 @@
         <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
         <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
         <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>20</v>
@@ -6544,10 +6544,10 @@
         <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO24" t="n">
         <v>60</v>
@@ -6559,10 +6559,10 @@
         <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -6595,22 +6595,22 @@
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF24" t="n">
         <v>9.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ24" t="n">
         <v>10</v>
@@ -6628,16 +6628,16 @@
         <v>4.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS24" t="n">
         <v>7.4</v>
@@ -6646,7 +6646,7 @@
         <v>8.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
@@ -6661,14 +6661,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA24" t="n">
         <v>7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -6717,31 +6717,31 @@
         <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O25" t="n">
         <v>1.05</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="S25" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
         <v>1.88</v>
@@ -6753,10 +6753,10 @@
         <v>1.61</v>
       </c>
       <c r="X25" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
         <v>25</v>
@@ -6864,65 +6864,65 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -6956,16 +6956,16 @@
         <v>1.46</v>
       </c>
       <c r="G26" t="n">
-        <v>2.82</v>
+        <v>1.63</v>
       </c>
       <c r="H26" t="n">
         <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
         <v>1.23</v>
@@ -6989,25 +6989,25 @@
         <v>1.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y26" t="n">
         <v>1000</v>
@@ -7109,74 +7109,74 @@
         <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -7363,10 +7363,10 @@
         <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H28" t="n">
         <v>4.1</v>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,22 +7485,22 @@
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.22</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
         <v>1.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7509,13 +7509,13 @@
         <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
         <v>1000</v>
@@ -7626,65 +7626,65 @@
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="G29" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="I29" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="J29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.21</v>
@@ -7745,28 +7745,28 @@
         <v>1.15</v>
       </c>
       <c r="P29" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="R29" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S29" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="T29" t="n">
         <v>1.53</v>
       </c>
       <c r="U29" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V29" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X29" t="n">
         <v>38</v>
@@ -7778,7 +7778,7 @@
         <v>17.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB29" t="n">
         <v>32</v>
@@ -7790,7 +7790,7 @@
         <v>13.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF29" t="n">
         <v>50</v>
@@ -7820,10 +7820,10 @@
         <v>36</v>
       </c>
       <c r="AO29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>11.5</v>
@@ -7847,7 +7847,7 @@
         <v>11.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY29" t="n">
         <v>14</v>
@@ -7859,16 +7859,16 @@
         <v>17</v>
       </c>
       <c r="BB29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC29" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC29" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF29" t="n">
         <v>21</v>
@@ -7877,10 +7877,10 @@
         <v>5</v>
       </c>
       <c r="BH29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ29" t="n">
         <v>9.199999999999999</v>
@@ -7892,13 +7892,13 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
@@ -7913,32 +7913,32 @@
         <v>7.8</v>
       </c>
       <c r="BT29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW29" t="n">
         <v>5.2</v>
       </c>
-      <c r="BU29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BW29" t="n">
+      <c r="BX29" t="n">
+        <v>19</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="CA29" t="n">
         <v>5.4</v>
       </c>
-      <c r="BX29" t="n">
-        <v>20</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>13</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>5.7</v>
-      </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -7978,10 +7978,10 @@
         <v>1.66</v>
       </c>
       <c r="I30" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J30" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K30" t="n">
         <v>5.1</v>
@@ -8017,7 +8017,7 @@
         <v>2.52</v>
       </c>
       <c r="V30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W30" t="n">
         <v>1.23</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G31" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="I31" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="J31" t="n">
         <v>4.2</v>
@@ -8247,22 +8247,22 @@
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O31" t="n">
         <v>1.12</v>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" t="n">
         <v>1.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="T31" t="n">
         <v>1.42</v>
@@ -8271,10 +8271,10 @@
         <v>2.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="X31" t="n">
         <v>48</v>
@@ -8286,7 +8286,7 @@
         <v>40</v>
       </c>
       <c r="AA31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
         <v>24</v>
@@ -8346,7 +8346,7 @@
         <v>14</v>
       </c>
       <c r="AU31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV31" t="n">
         <v>11.5</v>
@@ -8388,55 +8388,55 @@
         <v>5.5</v>
       </c>
       <c r="BI31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ31" t="n">
         <v>8.4</v>
       </c>
       <c r="BK31" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ31" t="n">
         <v>6.2</v>
       </c>
       <c r="BR31" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT31" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU31" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV31" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -8477,25 +8477,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>4.2</v>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M32" t="n">
         <v>1.02</v>
@@ -8507,7 +8507,7 @@
         <v>1.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q32" t="n">
         <v>1.45</v>
@@ -8516,19 +8516,19 @@
         <v>1.72</v>
       </c>
       <c r="S32" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T32" t="n">
         <v>1.44</v>
       </c>
       <c r="U32" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="V32" t="n">
         <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X32" t="n">
         <v>34</v>
@@ -8540,16 +8540,16 @@
         <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB32" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE32" t="n">
         <v>44</v>
@@ -8570,7 +8570,7 @@
         <v>23</v>
       </c>
       <c r="AK32" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL32" t="n">
         <v>26</v>
@@ -8579,22 +8579,22 @@
         <v>65</v>
       </c>
       <c r="AN32" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AO32" t="n">
         <v>28</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>18</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT32" t="n">
         <v>11</v>
@@ -8606,7 +8606,7 @@
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -8618,7 +8618,7 @@
         <v>11.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB32" t="n">
         <v>15.5</v>
@@ -8630,10 +8630,10 @@
         <v>17.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG32" t="n">
         <v>19</v>
@@ -8648,22 +8648,22 @@
         <v>9</v>
       </c>
       <c r="BK32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ32" t="n">
         <v>5.4</v>
@@ -8672,25 +8672,25 @@
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU32" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
         <v>2.04</v>
       </c>
       <c r="H33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I33" t="n">
         <v>4.4</v>
@@ -8833,7 +8833,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO33" t="n">
         <v>38</v>
@@ -8845,10 +8845,10 @@
         <v>14.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT33" t="n">
         <v>9.6</v>
@@ -8860,7 +8860,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX33" t="n">
         <v>11</v>
@@ -8872,7 +8872,7 @@
         <v>12</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB33" t="n">
         <v>17.5</v>
@@ -8884,13 +8884,13 @@
         <v>21</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF33" t="n">
         <v>7.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="n">
         <v>4.4</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
         <v>55</v>
       </c>
       <c r="AK34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL34" t="n">
         <v>42</v>
@@ -9108,7 +9108,7 @@
         <v>11</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV34" t="n">
         <v>9.199999999999999</v>
@@ -9126,19 +9126,19 @@
         <v>12</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC34" t="n">
         <v>4.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF34" t="n">
         <v>16.5</v>
@@ -9156,7 +9156,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK34" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
@@ -9168,7 +9168,7 @@
         <v>6.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
@@ -9186,7 +9186,7 @@
         <v>5.9</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
         <v>24</v>
       </c>
       <c r="AA35" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB35" t="n">
         <v>24</v>
@@ -9356,34 +9356,34 @@
         <v>14.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT35" t="n">
         <v>14.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV35" t="n">
         <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX35" t="n">
         <v>20</v>
       </c>
       <c r="AY35" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>10.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="BC35" t="n">
         <v>21</v>
@@ -9392,13 +9392,13 @@
         <v>21</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BF35" t="n">
         <v>11</v>
       </c>
       <c r="BG35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BH35" t="n">
         <v>5</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
         <v>7.4</v>
       </c>
       <c r="K36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.15</v>
@@ -9595,22 +9595,22 @@
         <v>120</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="AO36" t="n">
         <v>140</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT36" t="n">
         <v>12.5</v>
@@ -9619,10 +9619,10 @@
         <v>14</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX36" t="n">
         <v>10.5</v>
@@ -9634,7 +9634,7 @@
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB36" t="n">
         <v>8.6</v>
@@ -9646,13 +9646,13 @@
         <v>20</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF36" t="n">
         <v>2.72</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH36" t="n">
         <v>6.4</v>
@@ -9664,7 +9664,7 @@
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
@@ -9676,7 +9676,7 @@
         <v>4.5</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP36" t="n">
         <v>6.8</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -9750,13 +9750,13 @@
         <v>4.5</v>
       </c>
       <c r="G37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J37" t="n">
         <v>4.1</v>
@@ -9795,7 +9795,7 @@
         <v>2.52</v>
       </c>
       <c r="V37" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W37" t="n">
         <v>1.24</v>
@@ -9912,13 +9912,13 @@
         <v>4.8</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BJ37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK37" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9930,7 +9930,7 @@
         <v>9</v>
       </c>
       <c r="BO37" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP37" t="n">
         <v>34</v>
@@ -9954,7 +9954,7 @@
         <v>11</v>
       </c>
       <c r="BW37" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX37" t="n">
         <v>19.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -10004,13 +10004,13 @@
         <v>2.74</v>
       </c>
       <c r="G38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H38" t="n">
         <v>2.42</v>
       </c>
       <c r="I38" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="J38" t="n">
         <v>3</v>
@@ -10028,7 +10028,7 @@
         <v>3.4</v>
       </c>
       <c r="O38" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P38" t="n">
         <v>1.83</v>
@@ -10049,10 +10049,10 @@
         <v>2.06</v>
       </c>
       <c r="V38" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X38" t="n">
         <v>16</v>
@@ -10172,59 +10172,59 @@
         <v>10</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BN38" t="n">
         <v>6.4</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP38" t="n">
         <v>25</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR38" t="n">
         <v>38</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT38" t="n">
         <v>5.9</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV38" t="n">
         <v>22</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX38" t="n">
         <v>36</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ38" t="n">
         <v>30</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G39" t="n">
         <v>1.54</v>
       </c>
       <c r="H39" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I39" t="n">
         <v>10</v>
@@ -10282,22 +10282,22 @@
         <v>4.3</v>
       </c>
       <c r="O39" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P39" t="n">
         <v>2.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U39" t="n">
         <v>1.94</v>
@@ -10309,7 +10309,7 @@
         <v>2.84</v>
       </c>
       <c r="X39" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="Y39" t="n">
         <v>42</v>
@@ -10339,7 +10339,7 @@
         <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AI39" t="n">
         <v>110</v>
@@ -10354,13 +10354,13 @@
         <v>50</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN39" t="n">
         <v>7.4</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP39" t="n">
         <v>5.5</v>
@@ -10372,7 +10372,7 @@
         <v>6.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT39" t="n">
         <v>6</v>
@@ -10384,7 +10384,7 @@
         <v>5.8</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX39" t="n">
         <v>6</v>
@@ -10393,7 +10393,7 @@
         <v>7</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA39" t="n">
         <v>6.6</v>
@@ -10408,13 +10408,13 @@
         <v>5.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH39" t="n">
         <v>4.3</v>
@@ -10426,13 +10426,13 @@
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BN39" t="n">
         <v>4.3</v>
@@ -10444,41 +10444,41 @@
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -10539,22 +10539,22 @@
         <v>1.07</v>
       </c>
       <c r="P40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R40" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T40" t="n">
         <v>1.35</v>
       </c>
       <c r="U40" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V40" t="n">
         <v>1.18</v>
@@ -10566,7 +10566,7 @@
         <v>85</v>
       </c>
       <c r="Y40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z40" t="n">
         <v>80</v>
@@ -10608,7 +10608,7 @@
         <v>24</v>
       </c>
       <c r="AM40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN40" t="n">
         <v>4.4</v>
@@ -10644,7 +10644,7 @@
         <v>15</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
         <v>12</v>
@@ -10653,7 +10653,7 @@
         <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC40" t="n">
         <v>11</v>
@@ -10665,7 +10665,7 @@
         <v>4</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BG40" t="n">
         <v>15</v>
@@ -10674,65 +10674,65 @@
         <v>7.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL40" t="n">
         <v>48</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BN40" t="n">
         <v>6</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP40" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR40" t="n">
         <v>15.5</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT40" t="n">
         <v>11</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV40" t="n">
         <v>34</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX40" t="n">
         <v>28</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ40" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H41" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="J41" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10787,22 +10787,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O41" t="n">
         <v>1.1</v>
       </c>
       <c r="P41" t="n">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>1.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="S41" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="T41" t="n">
         <v>1.11</v>
@@ -10811,10 +10811,10 @@
         <v>1.11</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10928,65 +10928,65 @@
         <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN41" t="n">
         <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP41" t="n">
         <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT41" t="n">
         <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G43" t="n">
         <v>1.96</v>
@@ -11280,7 +11280,7 @@
         <v>3.65</v>
       </c>
       <c r="I43" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>4.5</v>
@@ -11319,7 +11319,7 @@
         <v>3.2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
         <v>2.04</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -11525,61 +11525,61 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G44" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I44" t="n">
         <v>3.4</v>
       </c>
       <c r="J44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L44" t="n">
         <v>1.42</v>
       </c>
       <c r="M44" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P44" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="R44" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T44" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U44" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V44" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W44" t="n">
         <v>1.6</v>
       </c>
       <c r="X44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
         <v>12.5</v>
@@ -11636,55 +11636,55 @@
         <v>9</v>
       </c>
       <c r="AQ44" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>16.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="AU44" t="n">
         <v>6.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX44" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA44" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB44" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB44" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC44" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE44" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF44" t="n">
         <v>5.9</v>
       </c>
-      <c r="BF44" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG44" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH44" t="n">
         <v>3.05</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -11788,10 +11788,10 @@
         <v>7.8</v>
       </c>
       <c r="I45" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J45" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K45" t="n">
         <v>4.2</v>
@@ -11812,7 +11812,7 @@
         <v>1.69</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
@@ -11824,10 +11824,10 @@
         <v>2.26</v>
       </c>
       <c r="U45" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V45" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W45" t="n">
         <v>2.6</v>
@@ -11893,7 +11893,7 @@
         <v>16.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS45" t="n">
         <v>8.800000000000001</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -12033,19 +12033,19 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G46" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H46" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I46" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K46" t="n">
         <v>4.1</v>
@@ -12084,7 +12084,7 @@
         <v>1.38</v>
       </c>
       <c r="W46" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X46" t="n">
         <v>24</v>
@@ -12111,7 +12111,7 @@
         <v>40</v>
       </c>
       <c r="AF46" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG46" t="n">
         <v>13</v>
@@ -12162,7 +12162,7 @@
         <v>11</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX46" t="n">
         <v>12.5</v>
@@ -12174,7 +12174,7 @@
         <v>11.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB46" t="n">
         <v>21</v>
@@ -12183,10 +12183,10 @@
         <v>16.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE46" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF46" t="n">
         <v>10</v>
@@ -12198,65 +12198,65 @@
         <v>4.2</v>
       </c>
       <c r="BI46" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BJ46" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK46" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL46" t="n">
         <v>90</v>
       </c>
       <c r="BM46" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN46" t="n">
         <v>5.5</v>
       </c>
       <c r="BO46" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP46" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ46" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BR46" t="n">
         <v>25</v>
       </c>
       <c r="BS46" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT46" t="n">
         <v>7.2</v>
       </c>
       <c r="BU46" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV46" t="n">
         <v>26</v>
       </c>
       <c r="BW46" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX46" t="n">
         <v>34</v>
       </c>
       <c r="BY46" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ46" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CA46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
         <v>1.45</v>
       </c>
       <c r="M47" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N47" t="n">
         <v>3.05</v>
@@ -12329,7 +12329,7 @@
         <v>4.2</v>
       </c>
       <c r="T47" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U47" t="n">
         <v>1.54</v>
@@ -12407,7 +12407,7 @@
         <v>4.9</v>
       </c>
       <c r="AT47" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU47" t="n">
         <v>8.6</v>
@@ -12419,7 +12419,7 @@
         <v>4.8</v>
       </c>
       <c r="AX47" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY47" t="n">
         <v>8.4</v>
@@ -12470,13 +12470,13 @@
         <v>3.55</v>
       </c>
       <c r="BO47" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BP47" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ47" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BR47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -12568,19 +12568,19 @@
         <v>2.9</v>
       </c>
       <c r="O48" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P48" t="n">
         <v>1.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R48" t="n">
         <v>1.24</v>
       </c>
       <c r="S48" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
         <v>1.95</v>
@@ -12637,7 +12637,7 @@
         <v>36</v>
       </c>
       <c r="AL48" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM48" t="n">
         <v>180</v>
@@ -12661,7 +12661,7 @@
         <v>4.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU48" t="n">
         <v>5.6</v>
@@ -12682,7 +12682,7 @@
         <v>15</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB48" t="n">
         <v>3.95</v>
@@ -12694,19 +12694,19 @@
         <v>4.1</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF48" t="n">
         <v>19.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH48" t="n">
         <v>2.98</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="BJ48" t="n">
         <v>11</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -12813,28 +12813,28 @@
         <v>4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M49" t="n">
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="O49" t="n">
         <v>1.37</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>1.73</v>
+        <v>2.74</v>
       </c>
       <c r="T49" t="n">
         <v>1.11</v>
@@ -12849,7 +12849,7 @@
         <v>2.38</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y49" t="n">
         <v>1000</v>
@@ -12951,74 +12951,74 @@
         <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ49" t="n">
         <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN49" t="n">
         <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT49" t="n">
         <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ49" t="n">
         <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -13049,28 +13049,28 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G50" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H50" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I50" t="n">
         <v>2.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L50" t="n">
         <v>1.48</v>
       </c>
       <c r="M50" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N50" t="n">
         <v>2.56</v>
@@ -13082,7 +13082,7 @@
         <v>1.51</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R50" t="n">
         <v>1.19</v>
@@ -13100,7 +13100,7 @@
         <v>1.71</v>
       </c>
       <c r="W50" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X50" t="n">
         <v>970</v>
@@ -13112,7 +13112,7 @@
         <v>970</v>
       </c>
       <c r="AA50" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB50" t="n">
         <v>970</v>
@@ -13133,7 +13133,7 @@
         <v>22</v>
       </c>
       <c r="AH50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI50" t="n">
         <v>75</v>
@@ -13154,67 +13154,67 @@
         <v>1000</v>
       </c>
       <c r="AO50" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ50" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR50" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT50" t="n">
         <v>3.55</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3.45</v>
       </c>
       <c r="AU50" t="n">
         <v>5.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AW50" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>2.68</v>
       </c>
-      <c r="AX50" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BA50" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BB50" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BF50" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BH50" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ50" t="n">
         <v>1000</v>
@@ -13256,23 +13256,23 @@
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -13303,10 +13303,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G51" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H51" t="n">
         <v>3.25</v>
@@ -13315,34 +13315,34 @@
         <v>4.1</v>
       </c>
       <c r="J51" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M51" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
         <v>1.42</v>
       </c>
       <c r="P51" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R51" t="n">
         <v>1.18</v>
       </c>
       <c r="S51" t="n">
-        <v>1.05</v>
+        <v>3.15</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -13354,7 +13354,7 @@
         <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X51" t="n">
         <v>970</v>
@@ -13363,7 +13363,7 @@
         <v>970</v>
       </c>
       <c r="Z51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA51" t="n">
         <v>90</v>
@@ -13411,16 +13411,16 @@
         <v>75</v>
       </c>
       <c r="AP51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ51" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT51" t="n">
         <v>6.2</v>
@@ -13432,7 +13432,7 @@
         <v>11</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX51" t="n">
         <v>10.5</v>
@@ -13441,92 +13441,92 @@
         <v>8.6</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -13560,22 +13560,22 @@
         <v>2.32</v>
       </c>
       <c r="G52" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="H52" t="n">
         <v>3.2</v>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J52" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K52" t="n">
         <v>3.55</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
@@ -13587,10 +13587,10 @@
         <v>1.4</v>
       </c>
       <c r="P52" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R52" t="n">
         <v>1.26</v>
@@ -13605,7 +13605,7 @@
         <v>1.96</v>
       </c>
       <c r="V52" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W52" t="n">
         <v>1.63</v>
@@ -13722,65 +13722,65 @@
         <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ52" t="n">
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
         <v>5.7</v>
       </c>
       <c r="H53" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I53" t="n">
         <v>2.2</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -14065,19 +14065,19 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="G54" t="n">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="H54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="I54" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="J54" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -14095,16 +14095,16 @@
         <v>1.06</v>
       </c>
       <c r="P54" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="Q54" t="n">
         <v>1.06</v>
       </c>
       <c r="R54" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="S54" t="n">
-        <v>1.06</v>
+        <v>1.58</v>
       </c>
       <c r="T54" t="n">
         <v>1.11</v>
@@ -14113,10 +14113,10 @@
         <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14221,74 +14221,74 @@
         <v>1.03</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ54" t="n">
         <v>1000</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN54" t="n">
         <v>1000</v>
       </c>
       <c r="BO54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP54" t="n">
         <v>1000</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT54" t="n">
         <v>1000</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -14349,16 +14349,16 @@
         <v>1.06</v>
       </c>
       <c r="P55" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q55" t="n">
         <v>1.06</v>
       </c>
       <c r="R55" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="S55" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="T55" t="n">
         <v>1.11</v>
@@ -14475,74 +14475,74 @@
         <v>1.03</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH55" t="n">
         <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ55" t="n">
         <v>1000</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN55" t="n">
         <v>1000</v>
       </c>
       <c r="BO55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP55" t="n">
         <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT55" t="n">
         <v>1000</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14585,7 @@
         <v>1.81</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K56" t="n">
         <v>10.5</v>
@@ -14606,13 +14606,13 @@
         <v>2.42</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R56" t="n">
         <v>1.65</v>
       </c>
       <c r="S56" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T56" t="n">
         <v>1.58</v>
@@ -14681,55 +14681,55 @@
         <v>970</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG56" t="n">
         <v>4.5</v>
@@ -14744,31 +14744,31 @@
         <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN56" t="n">
         <v>1000</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT56" t="n">
         <v>1000</v>
@@ -14780,23 +14780,23 @@
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -14830,10 +14830,10 @@
         <v>2.92</v>
       </c>
       <c r="G57" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H57" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I57" t="n">
         <v>2.52</v>
@@ -14878,7 +14878,7 @@
         <v>1.66</v>
       </c>
       <c r="W57" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X57" t="n">
         <v>20</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         <v>3.25</v>
       </c>
       <c r="H58" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I58" t="n">
         <v>2.34</v>
@@ -15144,7 +15144,7 @@
         <v>24</v>
       </c>
       <c r="AA58" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB58" t="n">
         <v>23</v>
@@ -15183,13 +15183,13 @@
         <v>55</v>
       </c>
       <c r="AN58" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AO58" t="n">
         <v>11</v>
       </c>
       <c r="AP58" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AQ58" t="n">
         <v>14.5</v>
@@ -15198,7 +15198,7 @@
         <v>16.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT58" t="n">
         <v>15</v>
@@ -15225,7 +15225,7 @@
         <v>20</v>
       </c>
       <c r="BB58" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC58" t="n">
         <v>18.5</v>
@@ -15234,7 +15234,7 @@
         <v>21</v>
       </c>
       <c r="BE58" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF58" t="n">
         <v>11</v>
@@ -15246,65 +15246,65 @@
         <v>1000</v>
       </c>
       <c r="BI58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ58" t="n">
         <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN58" t="n">
         <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP58" t="n">
         <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR58" t="n">
         <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT58" t="n">
         <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV58" t="n">
         <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX58" t="n">
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ58" t="n">
         <v>1000</v>
       </c>
       <c r="CA58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -15335,10 +15335,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G59" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H59" t="n">
         <v>4.1</v>
@@ -15428,7 +15428,7 @@
         <v>27</v>
       </c>
       <c r="AK59" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL59" t="n">
         <v>25</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -15592,19 +15592,19 @@
         <v>1.96</v>
       </c>
       <c r="G60" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H60" t="n">
         <v>3.05</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="J60" t="n">
         <v>2.7</v>
       </c>
       <c r="K60" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15640,115 +15640,115 @@
         <v>1.13</v>
       </c>
       <c r="W60" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X60" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA60" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AD60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ60" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM60" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO60" t="n">
         <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
         <v>2.52</v>
       </c>
       <c r="G61" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H61" t="n">
         <v>2.7</v>
@@ -15855,7 +15855,7 @@
         <v>3.6</v>
       </c>
       <c r="J61" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K61" t="n">
         <v>3.55</v>
@@ -15876,7 +15876,7 @@
         <v>1.46</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R61" t="n">
         <v>1.16</v>
@@ -15936,7 +15936,7 @@
         <v>60</v>
       </c>
       <c r="AK61" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL61" t="n">
         <v>1000</v>
@@ -15951,7 +15951,7 @@
         <v>75</v>
       </c>
       <c r="AP61" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ61" t="n">
         <v>3.45</v>
@@ -15960,7 +15960,7 @@
         <v>4.2</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AT61" t="n">
         <v>3.35</v>
@@ -15969,7 +15969,7 @@
         <v>3.15</v>
       </c>
       <c r="AV61" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AW61" t="n">
         <v>4.7</v>
@@ -15984,7 +15984,7 @@
         <v>4.3</v>
       </c>
       <c r="BA61" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BB61" t="n">
         <v>4.7</v>
@@ -15993,16 +15993,16 @@
         <v>4.6</v>
       </c>
       <c r="BD61" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.64</v>
+        <v>3.8</v>
       </c>
       <c r="BF61" t="n">
         <v>4.7</v>
       </c>
       <c r="BG61" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BH61" t="n">
         <v>2.96</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -16097,25 +16097,25 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G62" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I62" t="n">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="J62" t="n">
         <v>2.68</v>
       </c>
       <c r="K62" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M62" t="n">
         <v>1.09</v>
@@ -16124,13 +16124,13 @@
         <v>2.34</v>
       </c>
       <c r="O62" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="P62" t="n">
         <v>1.41</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="R62" t="n">
         <v>1.12</v>
@@ -16145,118 +16145,118 @@
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W62" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X62" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA62" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC62" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AD62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ62" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM62" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN62" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO62" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
         <v>1000</v>
       </c>
       <c r="J63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K63" t="n">
         <v>1000</v>
@@ -16507,10 +16507,10 @@
         <v>1.03</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
         <v>1000</v>
       </c>
       <c r="J64" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K64" t="n">
         <v>1000</v>
@@ -16761,10 +16761,10 @@
         <v>1.03</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -16865,13 +16865,13 @@
         <v>1000</v>
       </c>
       <c r="H65" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I65" t="n">
         <v>1000</v>
       </c>
       <c r="J65" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K65" t="n">
         <v>1000</v>
@@ -17015,10 +17015,10 @@
         <v>1.03</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH65" t="n">
         <v>1000</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -17269,10 +17269,10 @@
         <v>1.03</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG66" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH66" t="n">
         <v>1000</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17379,7 @@
         <v>1000</v>
       </c>
       <c r="J67" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K67" t="n">
         <v>1000</v>
@@ -17406,7 +17406,7 @@
         <v>1.12</v>
       </c>
       <c r="S67" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T67" t="n">
         <v>1.11</v>
@@ -17523,10 +17523,10 @@
         <v>1.03</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH67" t="n">
         <v>1000</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
         <v>1000</v>
       </c>
       <c r="J68" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K68" t="n">
         <v>1000</v>
@@ -17777,64 +17777,64 @@
         <v>1.03</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG68" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH68" t="n">
         <v>1000</v>
       </c>
       <c r="BI68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ68" t="n">
         <v>1000</v>
       </c>
       <c r="BK68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL68" t="n">
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN68" t="n">
         <v>1000</v>
       </c>
       <c r="BO68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP68" t="n">
         <v>1000</v>
       </c>
       <c r="BQ68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR68" t="n">
         <v>1000</v>
       </c>
       <c r="BS68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT68" t="n">
         <v>1000</v>
       </c>
       <c r="BU68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV68" t="n">
         <v>1000</v>
       </c>
       <c r="BW68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX68" t="n">
         <v>1000</v>
       </c>
       <c r="BY68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ68" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G69" t="n">
         <v>4</v>
@@ -17884,7 +17884,7 @@
         <v>2.14</v>
       </c>
       <c r="I69" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J69" t="n">
         <v>3.3</v>
@@ -17911,13 +17911,13 @@
         <v>2.06</v>
       </c>
       <c r="R69" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S69" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T69" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U69" t="n">
         <v>2.02</v>
@@ -17950,13 +17950,13 @@
         <v>13</v>
       </c>
       <c r="AE69" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF69" t="n">
         <v>32</v>
       </c>
       <c r="AG69" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH69" t="n">
         <v>22</v>
@@ -18016,28 +18016,28 @@
         <v>16</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB69" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD69" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC69" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD69" t="n">
+      <c r="BE69" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF69" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BE69" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF69" t="n">
-        <v>5.5</v>
       </c>
       <c r="BG69" t="n">
         <v>17.5</v>
       </c>
       <c r="BH69" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI69" t="n">
         <v>2.66</v>
@@ -18046,13 +18046,13 @@
         <v>10.5</v>
       </c>
       <c r="BK69" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
       </c>
       <c r="BM69" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN69" t="n">
         <v>7.2</v>
@@ -18064,16 +18064,16 @@
         <v>34</v>
       </c>
       <c r="BQ69" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR69" t="n">
         <v>46</v>
       </c>
       <c r="BS69" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU69" t="n">
         <v>3.95</v>
@@ -18082,23 +18082,23 @@
         <v>17.5</v>
       </c>
       <c r="BW69" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX69" t="n">
         <v>34</v>
       </c>
       <c r="BY69" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ69" t="n">
         <v>32</v>
       </c>
       <c r="CA69" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -18147,13 +18147,13 @@
         <v>3.4</v>
       </c>
       <c r="L70" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M70" t="n">
         <v>1.07</v>
       </c>
       <c r="N70" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O70" t="n">
         <v>1.3</v>
@@ -18171,16 +18171,16 @@
         <v>3.25</v>
       </c>
       <c r="T70" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U70" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V70" t="n">
         <v>1.37</v>
       </c>
       <c r="W70" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X70" t="n">
         <v>15</v>
@@ -18198,7 +18198,7 @@
         <v>11</v>
       </c>
       <c r="AC70" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD70" t="n">
         <v>15</v>
@@ -18210,7 +18210,7 @@
         <v>15</v>
       </c>
       <c r="AG70" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH70" t="n">
         <v>16</v>
@@ -18219,7 +18219,7 @@
         <v>55</v>
       </c>
       <c r="AJ70" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK70" t="n">
         <v>24</v>
@@ -18294,7 +18294,7 @@
         <v>1000</v>
       </c>
       <c r="BI70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -18395,13 +18395,13 @@
         <v>5.2</v>
       </c>
       <c r="J71" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K71" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L71" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M71" t="n">
         <v>1.09</v>
@@ -18413,19 +18413,19 @@
         <v>1.38</v>
       </c>
       <c r="P71" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R71" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="U71" t="n">
         <v>1.72</v>
@@ -18449,10 +18449,10 @@
         <v>150</v>
       </c>
       <c r="AB71" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC71" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD71" t="n">
         <v>24</v>
@@ -18497,22 +18497,22 @@
         <v>10.5</v>
       </c>
       <c r="AR71" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AS71" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT71" t="n">
         <v>6</v>
       </c>
       <c r="AU71" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="AV71" t="n">
         <v>14</v>
       </c>
       <c r="AW71" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AX71" t="n">
         <v>8.199999999999999</v>
@@ -18524,7 +18524,7 @@
         <v>15</v>
       </c>
       <c r="BA71" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB71" t="n">
         <v>16</v>
@@ -18533,16 +18533,16 @@
         <v>16.5</v>
       </c>
       <c r="BD71" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE71" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF71" t="n">
         <v>12</v>
       </c>
       <c r="BG71" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH71" t="n">
         <v>3.2</v>
@@ -18560,13 +18560,13 @@
         <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BN71" t="n">
         <v>4.5</v>
       </c>
       <c r="BO71" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP71" t="n">
         <v>1000</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G72" t="n">
         <v>2.68</v>
@@ -18646,7 +18646,7 @@
         <v>3.2</v>
       </c>
       <c r="I72" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>3.15</v>
@@ -18661,13 +18661,13 @@
         <v>1.12</v>
       </c>
       <c r="N72" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>1.54</v>
       </c>
       <c r="P72" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q72" t="n">
         <v>2.6</v>
@@ -18685,7 +18685,7 @@
         <v>1.77</v>
       </c>
       <c r="V72" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W72" t="n">
         <v>1.59</v>
@@ -18799,22 +18799,22 @@
         <v>5.5</v>
       </c>
       <c r="BH72" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI72" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ72" t="n">
         <v>11.5</v>
       </c>
       <c r="BK72" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL72" t="n">
         <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN72" t="n">
         <v>5.6</v>
@@ -18832,7 +18832,7 @@
         <v>1000</v>
       </c>
       <c r="BS72" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT72" t="n">
         <v>6.4</v>
@@ -18844,23 +18844,23 @@
         <v>32</v>
       </c>
       <c r="BW72" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX72" t="n">
         <v>55</v>
       </c>
       <c r="BY72" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ72" t="n">
         <v>55</v>
       </c>
       <c r="CA72" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -19056,65 +19056,65 @@
         <v>1000</v>
       </c>
       <c r="BI73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ73" t="n">
         <v>1000</v>
       </c>
       <c r="BK73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL73" t="n">
         <v>1000</v>
       </c>
       <c r="BM73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN73" t="n">
         <v>1000</v>
       </c>
       <c r="BO73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP73" t="n">
         <v>1000</v>
       </c>
       <c r="BQ73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR73" t="n">
         <v>1000</v>
       </c>
       <c r="BS73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT73" t="n">
         <v>1000</v>
       </c>
       <c r="BU73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV73" t="n">
         <v>1000</v>
       </c>
       <c r="BW73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX73" t="n">
         <v>1000</v>
       </c>
       <c r="BY73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ73" t="n">
         <v>1000</v>
       </c>
       <c r="CA73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -19145,28 +19145,28 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="G74" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="H74" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="I74" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="J74" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K74" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L74" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M74" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N74" t="n">
         <v>3</v>
@@ -19175,10 +19175,10 @@
         <v>1.41</v>
       </c>
       <c r="P74" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R74" t="n">
         <v>1.25</v>
@@ -19187,124 +19187,124 @@
         <v>4.2</v>
       </c>
       <c r="T74" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U74" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V74" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="W74" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X74" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB74" t="n">
         <v>13</v>
       </c>
-      <c r="Y74" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AC74" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD74" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE74" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF74" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG74" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH74" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI74" t="n">
         <v>60</v>
       </c>
       <c r="AJ74" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AK74" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN74" t="n">
         <v>55</v>
       </c>
-      <c r="AL74" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>65</v>
-      </c>
       <c r="AO74" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP74" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ74" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR74" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS74" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT74" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU74" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AV74" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW74" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AX74" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY74" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ74" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA74" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB74" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC74" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD74" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE74" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF74" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG74" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BH74" t="n">
         <v>1000</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -19399,16 +19399,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G75" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H75" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>2.98</v>
@@ -19417,22 +19417,22 @@
         <v>3.15</v>
       </c>
       <c r="L75" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M75" t="n">
         <v>1.14</v>
       </c>
       <c r="N75" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O75" t="n">
         <v>1.61</v>
       </c>
       <c r="P75" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R75" t="n">
         <v>1.17</v>
@@ -19444,19 +19444,19 @@
         <v>2.2</v>
       </c>
       <c r="U75" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V75" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W75" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X75" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z75" t="n">
         <v>30</v>
@@ -19465,19 +19465,19 @@
         <v>130</v>
       </c>
       <c r="AB75" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC75" t="n">
         <v>7.6</v>
       </c>
       <c r="AD75" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE75" t="n">
         <v>85</v>
       </c>
       <c r="AF75" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG75" t="n">
         <v>13</v>
@@ -19513,10 +19513,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR75" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS75" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT75" t="n">
         <v>5.8</v>
@@ -19528,7 +19528,7 @@
         <v>15.5</v>
       </c>
       <c r="AW75" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX75" t="n">
         <v>9.800000000000001</v>
@@ -19537,92 +19537,92 @@
         <v>10.5</v>
       </c>
       <c r="AZ75" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA75" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB75" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BC75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD75" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE75" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF75" t="n">
         <v>7</v>
       </c>
-      <c r="BF75" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG75" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH75" t="n">
         <v>1000</v>
       </c>
       <c r="BI75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ75" t="n">
         <v>1000</v>
       </c>
       <c r="BK75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL75" t="n">
         <v>1000</v>
       </c>
       <c r="BM75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN75" t="n">
         <v>1000</v>
       </c>
       <c r="BO75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP75" t="n">
         <v>1000</v>
       </c>
       <c r="BQ75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR75" t="n">
         <v>1000</v>
       </c>
       <c r="BS75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT75" t="n">
         <v>1000</v>
       </c>
       <c r="BU75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV75" t="n">
         <v>1000</v>
       </c>
       <c r="BW75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX75" t="n">
         <v>1000</v>
       </c>
       <c r="BY75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ75" t="n">
         <v>1000</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -19653,46 +19653,46 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="G76" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H76" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
         <v>1000</v>
       </c>
       <c r="J76" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K76" t="n">
         <v>1000</v>
       </c>
       <c r="L76" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M76" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="O76" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P76" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="R76" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S76" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T76" t="n">
         <v>1.11</v>
@@ -19704,7 +19704,7 @@
         <v>1.01</v>
       </c>
       <c r="W76" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -19809,74 +19809,74 @@
         <v>1.03</v>
       </c>
       <c r="BF76" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG76" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH76" t="n">
         <v>1000</v>
       </c>
       <c r="BI76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ76" t="n">
         <v>1000</v>
       </c>
       <c r="BK76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL76" t="n">
         <v>1000</v>
       </c>
       <c r="BM76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN76" t="n">
         <v>1000</v>
       </c>
       <c r="BO76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP76" t="n">
         <v>1000</v>
       </c>
       <c r="BQ76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR76" t="n">
         <v>1000</v>
       </c>
       <c r="BS76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT76" t="n">
         <v>1000</v>
       </c>
       <c r="BU76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV76" t="n">
         <v>1000</v>
       </c>
       <c r="BW76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX76" t="n">
         <v>1000</v>
       </c>
       <c r="BY76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ76" t="n">
         <v>1000</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -19907,46 +19907,46 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="G77" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H77" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="I77" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="J77" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="K77" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L77" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M77" t="n">
         <v>1.01</v>
       </c>
       <c r="N77" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O77" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="P77" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="R77" t="n">
         <v>1.14</v>
       </c>
       <c r="S77" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="T77" t="n">
         <v>1.11</v>
@@ -19955,13 +19955,13 @@
         <v>1.11</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="W77" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X77" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y77" t="n">
         <v>1000</v>
@@ -20063,74 +20063,74 @@
         <v>1.03</v>
       </c>
       <c r="BF77" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG77" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BH77" t="n">
         <v>1000</v>
       </c>
       <c r="BI77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ77" t="n">
         <v>1000</v>
       </c>
       <c r="BK77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL77" t="n">
         <v>1000</v>
       </c>
       <c r="BM77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN77" t="n">
         <v>1000</v>
       </c>
       <c r="BO77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP77" t="n">
         <v>1000</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR77" t="n">
         <v>1000</v>
       </c>
       <c r="BS77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT77" t="n">
         <v>1000</v>
       </c>
       <c r="BU77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV77" t="n">
         <v>1000</v>
       </c>
       <c r="BW77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX77" t="n">
         <v>1000</v>
       </c>
       <c r="BY77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ77" t="n">
         <v>1000</v>
       </c>
       <c r="CA77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20164,7 @@
         <v>1.57</v>
       </c>
       <c r="G78" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H78" t="n">
         <v>6.2</v>
@@ -20188,7 +20188,7 @@
         <v>4.8</v>
       </c>
       <c r="O78" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P78" t="n">
         <v>2.24</v>
@@ -20248,7 +20248,7 @@
         <v>24</v>
       </c>
       <c r="AI78" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ78" t="n">
         <v>17.5</v>
@@ -20311,7 +20311,7 @@
         <v>14</v>
       </c>
       <c r="BD78" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE78" t="n">
         <v>7.2</v>
@@ -20320,7 +20320,7 @@
         <v>6.8</v>
       </c>
       <c r="BG78" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH78" t="n">
         <v>3.95</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -20415,22 +20415,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="G79" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="H79" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="I79" t="n">
         <v>1000</v>
       </c>
       <c r="J79" t="n">
-        <v>1.78</v>
+        <v>1.09</v>
       </c>
       <c r="K79" t="n">
-        <v>7</v>
+        <v>500</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -20439,22 +20439,22 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="O79" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="P79" t="n">
         <v>1.3</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="R79" t="n">
         <v>1.12</v>
       </c>
       <c r="S79" t="n">
-        <v>2.08</v>
+        <v>1.05</v>
       </c>
       <c r="T79" t="n">
         <v>1.11</v>
@@ -20463,118 +20463,118 @@
         <v>1.11</v>
       </c>
       <c r="V79" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W79" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="X79" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA79" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC79" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AD79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ79" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM79" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN79" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO79" t="n">
         <v>1000</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AU79" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV79" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AX79" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BA79" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BD79" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BF79" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG79" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH79" t="n">
         <v>1000</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
         <v>2.72</v>
       </c>
       <c r="X80" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y80" t="n">
         <v>1000</v>
@@ -20834,65 +20834,65 @@
         <v>1000</v>
       </c>
       <c r="BI80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ80" t="n">
         <v>1000</v>
       </c>
       <c r="BK80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL80" t="n">
         <v>1000</v>
       </c>
       <c r="BM80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN80" t="n">
         <v>1000</v>
       </c>
       <c r="BO80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP80" t="n">
         <v>1000</v>
       </c>
       <c r="BQ80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR80" t="n">
         <v>1000</v>
       </c>
       <c r="BS80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT80" t="n">
         <v>1000</v>
       </c>
       <c r="BU80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV80" t="n">
         <v>1000</v>
       </c>
       <c r="BW80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX80" t="n">
         <v>1000</v>
       </c>
       <c r="BY80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ80" t="n">
         <v>1000</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G81" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I81" t="n">
         <v>4.2</v>
@@ -20938,7 +20938,7 @@
         <v>3.2</v>
       </c>
       <c r="K81" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -20959,22 +20959,22 @@
         <v>2.18</v>
       </c>
       <c r="R81" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S81" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T81" t="n">
         <v>1.9</v>
       </c>
       <c r="U81" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V81" t="n">
         <v>1.31</v>
       </c>
       <c r="W81" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X81" t="n">
         <v>13</v>
@@ -21013,7 +21013,7 @@
         <v>70</v>
       </c>
       <c r="AJ81" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK81" t="n">
         <v>28</v>
@@ -21025,7 +21025,7 @@
         <v>150</v>
       </c>
       <c r="AN81" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO81" t="n">
         <v>70</v>
@@ -21040,7 +21040,7 @@
         <v>20</v>
       </c>
       <c r="AS81" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT81" t="n">
         <v>7.2</v>
@@ -21052,7 +21052,7 @@
         <v>12.5</v>
       </c>
       <c r="AW81" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX81" t="n">
         <v>10</v>
@@ -21064,7 +21064,7 @@
         <v>17</v>
       </c>
       <c r="BA81" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB81" t="n">
         <v>6.6</v>
@@ -21073,80 +21073,80 @@
         <v>20</v>
       </c>
       <c r="BD81" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE81" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF81" t="n">
         <v>17</v>
       </c>
       <c r="BG81" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH81" t="n">
         <v>1000</v>
       </c>
       <c r="BI81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ81" t="n">
         <v>1000</v>
       </c>
       <c r="BK81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL81" t="n">
         <v>1000</v>
       </c>
       <c r="BM81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN81" t="n">
         <v>1000</v>
       </c>
       <c r="BO81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP81" t="n">
         <v>1000</v>
       </c>
       <c r="BQ81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR81" t="n">
         <v>1000</v>
       </c>
       <c r="BS81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT81" t="n">
         <v>1000</v>
       </c>
       <c r="BU81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV81" t="n">
         <v>1000</v>
       </c>
       <c r="BW81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX81" t="n">
         <v>1000</v>
       </c>
       <c r="BY81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ81" t="n">
         <v>1000</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -21189,10 +21189,10 @@
         <v>4.2</v>
       </c>
       <c r="J82" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K82" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -21201,28 +21201,28 @@
         <v>1.13</v>
       </c>
       <c r="N82" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O82" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P82" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R82" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S82" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T82" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U82" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V82" t="n">
         <v>1.32</v>
@@ -21264,7 +21264,7 @@
         <v>28</v>
       </c>
       <c r="AI82" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ82" t="n">
         <v>42</v>
@@ -21279,10 +21279,10 @@
         <v>230</v>
       </c>
       <c r="AN82" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO82" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP82" t="n">
         <v>7.2</v>
@@ -21294,7 +21294,7 @@
         <v>19.5</v>
       </c>
       <c r="AS82" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT82" t="n">
         <v>6.4</v>
@@ -21303,10 +21303,10 @@
         <v>6</v>
       </c>
       <c r="AV82" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW82" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX82" t="n">
         <v>9.800000000000001</v>
@@ -21315,28 +21315,28 @@
         <v>10</v>
       </c>
       <c r="AZ82" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA82" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB82" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC82" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC82" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD82" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE82" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG82" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF82" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG82" t="n">
-        <v>5</v>
       </c>
       <c r="BH82" t="n">
         <v>1000</v>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -21437,7 +21437,7 @@
         <v>1.79</v>
       </c>
       <c r="H83" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I83" t="n">
         <v>6.2</v>
@@ -21455,7 +21455,7 @@
         <v>1.01</v>
       </c>
       <c r="N83" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="O83" t="n">
         <v>1.16</v>
@@ -21464,19 +21464,19 @@
         <v>2.38</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="R83" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S83" t="n">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="T83" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U83" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V83" t="n">
         <v>1.19</v>
@@ -21485,7 +21485,7 @@
         <v>2.26</v>
       </c>
       <c r="X83" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y83" t="n">
         <v>1000</v>
@@ -21587,10 +21587,10 @@
         <v>1.03</v>
       </c>
       <c r="BF83" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BG83" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BH83" t="n">
         <v>1000</v>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -21688,22 +21688,22 @@
         <v>2.02</v>
       </c>
       <c r="G84" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H84" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I84" t="n">
         <v>5.8</v>
       </c>
       <c r="J84" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K84" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L84" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M84" t="n">
         <v>1.14</v>
@@ -21718,7 +21718,7 @@
         <v>1.43</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="R84" t="n">
         <v>1.17</v>
@@ -21850,65 +21850,65 @@
         <v>1000</v>
       </c>
       <c r="BI84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ84" t="n">
         <v>1000</v>
       </c>
       <c r="BK84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL84" t="n">
         <v>1000</v>
       </c>
       <c r="BM84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN84" t="n">
         <v>1000</v>
       </c>
       <c r="BO84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP84" t="n">
         <v>1000</v>
       </c>
       <c r="BQ84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR84" t="n">
         <v>1000</v>
       </c>
       <c r="BS84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT84" t="n">
         <v>1000</v>
       </c>
       <c r="BU84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV84" t="n">
         <v>1000</v>
       </c>
       <c r="BW84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX84" t="n">
         <v>1000</v>
       </c>
       <c r="BY84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ84" t="n">
         <v>1000</v>
       </c>
       <c r="CA84" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -21942,7 +21942,7 @@
         <v>1.97</v>
       </c>
       <c r="G85" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H85" t="n">
         <v>4.5</v>
@@ -21951,13 +21951,13 @@
         <v>5.6</v>
       </c>
       <c r="J85" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K85" t="n">
         <v>3.4</v>
       </c>
       <c r="L85" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="M85" t="n">
         <v>1.15</v>
@@ -21990,7 +21990,7 @@
         <v>1.22</v>
       </c>
       <c r="W85" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="X85" t="n">
         <v>8.6</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-14.xlsx
@@ -983,16 +983,16 @@
         <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ2" t="n">
         <v>5.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>130</v>
@@ -1231,7 +1231,7 @@
         <v>5.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
         <v>5.1</v>
@@ -1243,28 +1243,28 @@
         <v>5.7</v>
       </c>
       <c r="AX3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
         <v>5.3</v>
@@ -1276,7 +1276,7 @@
         <v>12.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>1.19</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU3" t="n">
         <v>3.75</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>1.69</v>
@@ -1377,7 +1377,7 @@
         <v>1.87</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
         <v>5.4</v>
@@ -1416,7 +1416,7 @@
         <v>2.14</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1437,7 +1437,7 @@
         <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
@@ -1473,7 +1473,7 @@
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.4</v>
@@ -1485,7 +1485,7 @@
         <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU4" t="n">
         <v>5.6</v>
@@ -1497,7 +1497,7 @@
         <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
@@ -1506,19 +1506,19 @@
         <v>10.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
@@ -1527,10 +1527,10 @@
         <v>6</v>
       </c>
       <c r="BH4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
@@ -1563,7 +1563,7 @@
         <v>1.48</v>
       </c>
       <c r="BT4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
         <v>3.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1652,19 +1652,19 @@
         <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
         <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
         <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
@@ -1673,7 +1673,7 @@
         <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1685,10 +1685,10 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1727,25 +1727,25 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
         <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
         <v>6.8</v>
@@ -1754,13 +1754,13 @@
         <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>9</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>6.2</v>
@@ -1769,16 +1769,16 @@
         <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="n">
         <v>4.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G6" t="n">
         <v>3.45</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="H6" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1942,7 +1942,7 @@
         <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1954,7 +1954,7 @@
         <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
         <v>19.5</v>
@@ -1963,19 +1963,19 @@
         <v>40</v>
       </c>
       <c r="AJ6" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
         <v>16</v>
@@ -1984,119 +1984,119 @@
         <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT6" t="n">
         <v>13</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>18.5</v>
       </c>
       <c r="AX6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF6" t="n">
         <v>20</v>
       </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>7</v>
-      </c>
       <c r="BO6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT6" t="n">
         <v>5.3</v>
       </c>
-      <c r="BP6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BU6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
         <v>15.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
         <v>27</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
         <v>2.12</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.27</v>
@@ -2178,10 +2178,10 @@
         <v>1.89</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
         <v>19.5</v>
@@ -2193,7 +2193,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
         <v>19</v>
@@ -2244,10 +2244,10 @@
         <v>7.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
@@ -2259,7 +2259,7 @@
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY7" t="n">
         <v>8.4</v>
@@ -2268,22 +2268,22 @@
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG7" t="n">
         <v>7.8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -2543,16 +2543,16 @@
         <v>32</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,47 +2564,47 @@
         <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR8" t="n">
         <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
         <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>29</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>44</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>34</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
         <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
         <v>3.3</v>
@@ -2677,7 +2677,7 @@
         <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
         <v>1.85</v>
@@ -2788,7 +2788,7 @@
         <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
         <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
         <v>2.18</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
         <v>1.91</v>
@@ -3203,7 +3203,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA11" t="n">
         <v>14</v>
@@ -3287,19 +3287,19 @@
         <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BD11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE11" t="n">
-        <v>9</v>
-      </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG11" t="n">
         <v>6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>1.76</v>
       </c>
       <c r="G12" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
@@ -3415,7 +3415,7 @@
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3430,7 +3430,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R12" t="n">
         <v>1.43</v>
@@ -3439,22 +3439,22 @@
         <v>2.98</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
         <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
         <v>46</v>
@@ -3463,13 +3463,13 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE12" t="n">
         <v>130</v>
@@ -3502,19 +3502,19 @@
         <v>12.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3523,40 +3523,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
         <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH12" t="n">
         <v>3.8</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
         <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
@@ -3681,10 +3681,10 @@
         <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
         <v>1.21</v>
@@ -3696,13 +3696,13 @@
         <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
         <v>10.5</v>
@@ -3729,7 +3729,7 @@
         <v>240</v>
       </c>
       <c r="AF13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
@@ -3741,7 +3741,7 @@
         <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="AK13" t="n">
         <v>100</v>
@@ -3756,10 +3756,10 @@
         <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>170</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>10.5</v>
@@ -3768,10 +3768,10 @@
         <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3780,7 +3780,7 @@
         <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>9</v>
@@ -3789,10 +3789,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
         <v>17.5</v>
@@ -3801,16 +3801,16 @@
         <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
         <v>15.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="n">
         <v>2.96</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>2.62</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.65</v>
@@ -3935,7 +3935,7 @@
         <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
         <v>2.06</v>
@@ -3956,16 +3956,16 @@
         <v>1.61</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>44</v>
@@ -3974,10 +3974,10 @@
         <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
         <v>36</v>
@@ -3986,16 +3986,16 @@
         <v>28</v>
       </c>
       <c r="AG14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
         <v>55</v>
@@ -4022,7 +4022,7 @@
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
         <v>10</v>
@@ -4046,22 +4046,22 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.7</v>
+        <v>26</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BG14" t="n">
         <v>21</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>1.87</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
         <v>7.6</v>
@@ -4174,16 +4174,16 @@
         <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="O15" t="n">
         <v>1.43</v>
@@ -4198,10 +4198,10 @@
         <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
         <v>1.74</v>
@@ -4219,7 +4219,7 @@
         <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4228,13 +4228,13 @@
         <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF15" t="n">
         <v>28</v>
@@ -4246,7 +4246,7 @@
         <v>85</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ15" t="n">
         <v>900</v>
@@ -4255,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="AL15" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
@@ -4264,19 +4264,19 @@
         <v>85</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP15" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
         <v>4.2</v>
@@ -4285,46 +4285,46 @@
         <v>4.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
         <v>5.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC15" t="n">
         <v>4</v>
       </c>
-      <c r="BB15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF15" t="n">
         <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="n">
         <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>2.9</v>
@@ -4437,16 +4437,16 @@
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.44</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.42</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -4455,10 +4455,10 @@
         <v>5.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
         <v>1.25</v>
@@ -4470,7 +4470,7 @@
         <v>9.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
         <v>80</v>
@@ -4482,22 +4482,22 @@
         <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
         <v>210</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
         <v>130</v>
@@ -4515,64 +4515,64 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
         <v>2.7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G17" t="n">
         <v>3.2</v>
@@ -4691,28 +4691,28 @@
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.44</v>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.89</v>
       </c>
       <c r="V17" t="n">
         <v>1.48</v>
@@ -4733,7 +4733,7 @@
         <v>50</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
         <v>7.6</v>
@@ -4742,7 +4742,7 @@
         <v>13.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
@@ -4769,67 +4769,67 @@
         <v>160</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO17" t="n">
         <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AS17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AV17" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF17" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI17" t="n">
         <v>2.64</v>
@@ -4838,59 +4838,59 @@
         <v>11</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="BN17" t="n">
         <v>6</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP17" t="n">
         <v>26</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT17" t="n">
         <v>5.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV17" t="n">
         <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="BX17" t="n">
         <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
         <v>42</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
         <v>2.22</v>
@@ -4939,7 +4939,7 @@
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
@@ -5029,7 +5029,7 @@
         <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>13.5</v>
@@ -5044,7 +5044,7 @@
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>11.5</v>
@@ -5053,7 +5053,7 @@
         <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -5175,64 +5175,64 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.22</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.16</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z19" t="n">
         <v>500</v>
@@ -5241,22 +5241,22 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC19" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
         <v>950</v>
@@ -5274,131 +5274,131 @@
         <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.06</v>
+        <v>4.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.07</v>
+        <v>4.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.07</v>
+        <v>5.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.07</v>
+        <v>6.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.07</v>
+        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.07</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.07</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.07</v>
+        <v>4.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.07</v>
+        <v>4.7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.07</v>
+        <v>5.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.07</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.07</v>
+        <v>5.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.07</v>
+        <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.07</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.07</v>
+        <v>4.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -5432,10 +5432,10 @@
         <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I20" t="n">
         <v>9.6</v>
@@ -5447,212 +5447,212 @@
         <v>5.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
         <v>2.42</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB20" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>75</v>
+        <v>15.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>29</v>
+        <v>5.7</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.23</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.23</v>
+        <v>6.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.23</v>
+        <v>7.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.19</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.23</v>
+        <v>6.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.23</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.19</v>
+        <v>7.8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.23</v>
+        <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.23</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.23</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.18</v>
+        <v>4.2</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>2.22</v>
@@ -5701,7 +5701,7 @@
         <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
@@ -5725,16 +5725,16 @@
         <v>2.16</v>
       </c>
       <c r="T21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
         <v>2.66</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X21" t="n">
         <v>32</v>
@@ -5845,68 +5845,68 @@
         <v>15</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
         <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
@@ -6099,68 +6099,68 @@
         <v>5.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H23" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>3.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
@@ -6224,10 +6224,10 @@
         <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
         <v>2.74</v>
@@ -6242,7 +6242,7 @@
         <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X23" t="n">
         <v>23</v>
@@ -6263,13 +6263,13 @@
         <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>75</v>
       </c>
       <c r="AF23" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
         <v>16.5</v>
@@ -6278,13 +6278,13 @@
         <v>17.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="n">
         <v>130</v>
       </c>
       <c r="AK23" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AL23" t="n">
         <v>75</v>
@@ -6293,13 +6293,13 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AO23" t="n">
         <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
@@ -6308,7 +6308,7 @@
         <v>18.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -6320,37 +6320,37 @@
         <v>7.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
         <v>8.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="n">
         <v>3.95</v>
@@ -6362,7 +6362,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6371,16 +6371,16 @@
         <v>13</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6389,16 +6389,16 @@
         <v>9.6</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G24" t="n">
         <v>1.94</v>
@@ -6454,7 +6454,7 @@
         <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>3.8</v>
@@ -6463,7 +6463,7 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -6481,7 +6481,7 @@
         <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -6493,7 +6493,7 @@
         <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
         <v>2.06</v>
@@ -6550,7 +6550,7 @@
         <v>11.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>270</v>
+        <v>600</v>
       </c>
       <c r="AP24" t="n">
         <v>14.5</v>
@@ -6574,7 +6574,7 @@
         <v>15.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -6586,7 +6586,7 @@
         <v>15.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="BB24" t="n">
         <v>17.5</v>
@@ -6604,71 +6604,71 @@
         <v>9.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ24" t="n">
         <v>10</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN24" t="n">
         <v>4.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BP24" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BR24" t="n">
         <v>27</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT24" t="n">
         <v>8.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>8.4</v>
       </c>
       <c r="BZ24" t="n">
         <v>22</v>
       </c>
       <c r="CA24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -6729,13 +6729,13 @@
         <v>1.05</v>
       </c>
       <c r="P25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
         <v>3.25</v>
@@ -6816,7 +6816,7 @@
         <v>5.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT25" t="n">
         <v>3.9</v>
@@ -6828,7 +6828,7 @@
         <v>4.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX25" t="n">
         <v>4.6</v>
@@ -6840,7 +6840,7 @@
         <v>4.9</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB25" t="n">
         <v>5.5</v>
@@ -6852,13 +6852,13 @@
         <v>5.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF25" t="n">
         <v>5.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -7007,10 +7007,10 @@
         <v>2.58</v>
       </c>
       <c r="X26" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y26" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
         <v>220</v>
@@ -7025,7 +7025,7 @@
         <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
         <v>400</v>
@@ -7037,7 +7037,7 @@
         <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
         <v>320</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>1.51</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
         <v>2.2</v>
@@ -7258,13 +7258,13 @@
         <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="X27" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y27" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="Z27" t="n">
         <v>90</v>
@@ -7273,13 +7273,13 @@
         <v>470</v>
       </c>
       <c r="AB27" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AC27" t="n">
         <v>42</v>
       </c>
       <c r="AD27" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
         <v>160</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
         <v>3.7</v>
@@ -7515,10 +7515,10 @@
         <v>2.42</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y28" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
         <v>220</v>
@@ -7533,7 +7533,7 @@
         <v>42</v>
       </c>
       <c r="AD28" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE28" t="n">
         <v>400</v>
@@ -7545,7 +7545,7 @@
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
         <v>320</v>
@@ -7581,10 +7581,10 @@
         <v>1.87</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.67</v>
+        <v>5.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="AV28" t="n">
         <v>1.79</v>
@@ -7596,7 +7596,7 @@
         <v>1.7</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.79</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
         <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="R30" t="n">
         <v>1.73</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>1.99</v>
       </c>
       <c r="G31" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H31" t="n">
         <v>3.45</v>
@@ -8271,10 +8271,10 @@
         <v>2.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X31" t="n">
         <v>48</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -8501,10 +8501,10 @@
         <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P32" t="n">
         <v>2.94</v>
@@ -8516,13 +8516,13 @@
         <v>1.84</v>
       </c>
       <c r="S32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
         <v>1.5</v>
       </c>
       <c r="U32" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V32" t="n">
         <v>1.27</v>
@@ -8531,10 +8531,10 @@
         <v>2.14</v>
       </c>
       <c r="X32" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Y32" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Z32" t="n">
         <v>140</v>
@@ -8642,7 +8642,7 @@
         <v>5.3</v>
       </c>
       <c r="BI32" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BJ32" t="n">
         <v>9</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK33" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
@@ -8935,13 +8935,13 @@
         <v>4.9</v>
       </c>
       <c r="BV33" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
         <v>6.4</v>
       </c>
       <c r="BX33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
         <v>7.2</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G34" t="n">
         <v>2.04</v>
@@ -9015,13 +9015,13 @@
         <v>1.22</v>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S34" t="n">
         <v>2.62</v>
@@ -9030,7 +9030,7 @@
         <v>1.63</v>
       </c>
       <c r="U34" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V34" t="n">
         <v>1.3</v>
@@ -9150,7 +9150,7 @@
         <v>4.3</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>2.3</v>
       </c>
       <c r="I35" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J35" t="n">
         <v>3.85</v>
@@ -9287,7 +9287,7 @@
         <v>2.7</v>
       </c>
       <c r="V35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W35" t="n">
         <v>1.48</v>
@@ -9302,7 +9302,7 @@
         <v>24</v>
       </c>
       <c r="AA35" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AB35" t="n">
         <v>21</v>
@@ -9371,7 +9371,7 @@
         <v>17.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AY35" t="n">
         <v>11.5</v>
@@ -9383,7 +9383,7 @@
         <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>34</v>
+        <v>6.4</v>
       </c>
       <c r="BC35" t="n">
         <v>21</v>
@@ -9392,7 +9392,7 @@
         <v>21</v>
       </c>
       <c r="BE35" t="n">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BF35" t="n">
         <v>11</v>
@@ -9410,7 +9410,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK35" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="G36" t="n">
         <v>1.28</v>
@@ -9604,7 +9604,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AR36" t="n">
         <v>6.8</v>
@@ -9637,7 +9637,7 @@
         <v>6.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC36" t="n">
         <v>9.800000000000001</v>
@@ -9664,7 +9664,7 @@
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
@@ -9676,13 +9676,13 @@
         <v>4.5</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BP36" t="n">
         <v>7</v>
       </c>
       <c r="BQ36" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR36" t="n">
         <v>17.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
         <v>2.24</v>
       </c>
       <c r="T37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U37" t="n">
         <v>2.52</v>
@@ -9852,7 +9852,7 @@
         <v>44</v>
       </c>
       <c r="AO37" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP37" t="n">
         <v>21</v>
@@ -9864,7 +9864,7 @@
         <v>11.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT37" t="n">
         <v>14.5</v>
@@ -9891,7 +9891,7 @@
         <v>21</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC37" t="n">
         <v>27</v>
@@ -9900,10 +9900,10 @@
         <v>30</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG37" t="n">
         <v>6</v>
@@ -9918,34 +9918,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK37" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN37" t="n">
         <v>9</v>
       </c>
       <c r="BO37" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP37" t="n">
         <v>34</v>
       </c>
       <c r="BQ37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR37" t="n">
         <v>36</v>
       </c>
       <c r="BS37" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU37" t="n">
         <v>4.3</v>
@@ -9954,13 +9954,13 @@
         <v>11</v>
       </c>
       <c r="BW37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BX37" t="n">
         <v>19.5</v>
       </c>
       <c r="BY37" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>1.42</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H39" t="n">
         <v>6.4</v>
@@ -10306,7 +10306,7 @@
         <v>1.12</v>
       </c>
       <c r="W39" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X39" t="n">
         <v>90</v>
@@ -10357,22 +10357,22 @@
         <v>140</v>
       </c>
       <c r="AN39" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AO39" t="n">
         <v>150</v>
       </c>
       <c r="AP39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT39" t="n">
         <v>5.6</v>
@@ -10393,22 +10393,22 @@
         <v>6.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA39" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BB39" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE39" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF39" t="n">
         <v>4.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="G40" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="H40" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="K40" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="L40" t="n">
         <v>1.13</v>
@@ -10539,55 +10539,55 @@
         <v>1.07</v>
       </c>
       <c r="P40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q40" t="n">
         <v>1.22</v>
       </c>
       <c r="R40" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="S40" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="T40" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U40" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="V40" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="W40" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="X40" t="n">
         <v>85</v>
       </c>
       <c r="Y40" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Z40" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AA40" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AB40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC40" t="n">
         <v>22</v>
       </c>
       <c r="AD40" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE40" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AF40" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG40" t="n">
         <v>16</v>
@@ -10596,37 +10596,37 @@
         <v>21</v>
       </c>
       <c r="AI40" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AJ40" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AK40" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM40" t="n">
         <v>46</v>
       </c>
       <c r="AN40" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AO40" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT40" t="n">
         <v>19</v>
@@ -10638,22 +10638,22 @@
         <v>17.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX40" t="n">
         <v>15</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BC40" t="n">
         <v>11</v>
@@ -10662,77 +10662,77 @@
         <v>14</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="BG40" t="n">
         <v>17</v>
       </c>
       <c r="BH40" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BI40" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BJ40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP40" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>48</v>
-      </c>
-      <c r="BM40" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN40" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP40" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BQ40" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BS40" t="n">
         <v>5.3</v>
       </c>
       <c r="BT40" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BU40" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV40" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY40" t="n">
         <v>6.6</v>
       </c>
-      <c r="BX40" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BZ40" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CA40" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G42" t="n">
         <v>2.58</v>
@@ -11095,13 +11095,13 @@
         <v>190</v>
       </c>
       <c r="AF42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG42" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI42" t="n">
         <v>130</v>
@@ -11179,16 +11179,16 @@
         <v>7.2</v>
       </c>
       <c r="BH42" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ42" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G43" t="n">
         <v>1.95</v>
@@ -11304,13 +11304,13 @@
         <v>3.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="R43" t="n">
         <v>2.06</v>
       </c>
       <c r="S43" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="T43" t="n">
         <v>1.37</v>
@@ -11379,58 +11379,58 @@
         <v>18</v>
       </c>
       <c r="AP43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR43" t="n">
         <v>29</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>16.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV43" t="n">
         <v>9</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX43" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ43" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BF43" t="n">
         <v>5.2</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH43" t="n">
         <v>5.8</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H44" t="n">
         <v>3.2</v>
@@ -11543,40 +11543,40 @@
         <v>3.3</v>
       </c>
       <c r="L44" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O44" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P44" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T44" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U44" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V44" t="n">
         <v>1.42</v>
       </c>
       <c r="W44" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X44" t="n">
         <v>12</v>
@@ -11639,10 +11639,10 @@
         <v>6.2</v>
       </c>
       <c r="AR44" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT44" t="n">
         <v>7.8</v>
@@ -11651,40 +11651,40 @@
         <v>6.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ44" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BB44" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BC44" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE44" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF44" t="n">
         <v>5.9</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH44" t="n">
         <v>3.05</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>1.56</v>
       </c>
       <c r="G45" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H45" t="n">
         <v>7.8</v>
@@ -11791,7 +11791,7 @@
         <v>9</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K45" t="n">
         <v>4.2</v>
@@ -11803,19 +11803,19 @@
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
         <v>1.42</v>
       </c>
       <c r="P45" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q45" t="n">
         <v>2.38</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S45" t="n">
         <v>4.4</v>
@@ -11824,16 +11824,16 @@
         <v>2.26</v>
       </c>
       <c r="U45" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V45" t="n">
         <v>1.12</v>
       </c>
       <c r="W45" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X45" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y45" t="n">
         <v>21</v>
@@ -11881,7 +11881,7 @@
         <v>580</v>
       </c>
       <c r="AN45" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO45" t="n">
         <v>340</v>
@@ -11890,25 +11890,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ45" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT45" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU45" t="n">
         <v>7.8</v>
       </c>
       <c r="AV45" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX45" t="n">
         <v>7</v>
@@ -11917,10 +11917,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA45" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB45" t="n">
         <v>12.5</v>
@@ -11929,34 +11929,34 @@
         <v>17</v>
       </c>
       <c r="BD45" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF45" t="n">
         <v>10.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH45" t="n">
         <v>3.2</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK45" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN45" t="n">
         <v>3.9</v>
@@ -11965,44 +11965,44 @@
         <v>3</v>
       </c>
       <c r="BP45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ45" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR45" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT45" t="n">
         <v>12</v>
       </c>
       <c r="BU45" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ45" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -12033,28 +12033,28 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G46" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H46" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J46" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K46" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L46" t="n">
         <v>1.31</v>
       </c>
       <c r="M46" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N46" t="n">
         <v>4.8</v>
@@ -12066,7 +12066,7 @@
         <v>2.32</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R46" t="n">
         <v>1.52</v>
@@ -12075,67 +12075,67 @@
         <v>2.66</v>
       </c>
       <c r="T46" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U46" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W46" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="X46" t="n">
         <v>22</v>
       </c>
       <c r="Y46" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA46" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB46" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD46" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE46" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF46" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ46" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK46" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL46" t="n">
         <v>32</v>
       </c>
       <c r="AM46" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AN46" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AO46" t="n">
         <v>28</v>
@@ -12150,13 +12150,13 @@
         <v>19.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AT46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU46" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV46" t="n">
         <v>11</v>
@@ -12168,7 +12168,7 @@
         <v>12.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ46" t="n">
         <v>11.5</v>
@@ -12186,16 +12186,16 @@
         <v>14.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG46" t="n">
         <v>18.5</v>
       </c>
       <c r="BH46" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI46" t="n">
         <v>3.55</v>
@@ -12204,13 +12204,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK46" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL46" t="n">
         <v>90</v>
       </c>
       <c r="BM46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN46" t="n">
         <v>5.5</v>
@@ -12222,41 +12222,41 @@
         <v>15</v>
       </c>
       <c r="BQ46" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR46" t="n">
         <v>25</v>
       </c>
       <c r="BS46" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT46" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU46" t="n">
         <v>6</v>
       </c>
       <c r="BV46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW46" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX46" t="n">
         <v>34</v>
       </c>
       <c r="BY46" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ46" t="n">
         <v>17.5</v>
       </c>
       <c r="CA46" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12383,7 @@
         <v>23</v>
       </c>
       <c r="AL47" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM47" t="n">
         <v>410</v>
@@ -12452,7 +12452,7 @@
         <v>3.2</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="BJ47" t="n">
         <v>15</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
         <v>3.45</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
@@ -12670,7 +12670,7 @@
         <v>14</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="AX48" t="n">
         <v>11.5</v>
@@ -12691,7 +12691,7 @@
         <v>13</v>
       </c>
       <c r="BD48" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BE48" t="n">
         <v>4.5</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -12816,31 +12816,31 @@
         <v>1.36</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="O49" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S49" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="T49" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V49" t="n">
         <v>1.17</v>
@@ -12849,112 +12849,112 @@
         <v>2.34</v>
       </c>
       <c r="X49" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="Y49" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="Z49" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AA49" t="n">
         <v>900</v>
       </c>
       <c r="AB49" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="AD49" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AG49" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH49" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ49" t="n">
-        <v>900</v>
+        <v>18.5</v>
       </c>
       <c r="AK49" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="AL49" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.24</v>
+        <v>9</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.25</v>
+        <v>14.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.25</v>
+        <v>30</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.22</v>
+        <v>7.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.25</v>
+        <v>20</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.26</v>
+        <v>7.6</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.24</v>
+        <v>15</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.26</v>
+        <v>7.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.25</v>
+        <v>15</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.24</v>
+        <v>17.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.25</v>
+        <v>28</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -13064,7 +13064,7 @@
         <v>2.88</v>
       </c>
       <c r="K50" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L50" t="n">
         <v>1.48</v>
@@ -13103,7 +13103,7 @@
         <v>1.28</v>
       </c>
       <c r="X50" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y50" t="n">
         <v>970</v>
@@ -13166,7 +13166,7 @@
         <v>4.8</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AT50" t="n">
         <v>4.8</v>
@@ -13175,40 +13175,40 @@
         <v>5.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.96</v>
+        <v>2.52</v>
       </c>
       <c r="AX50" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AY50" t="n">
         <v>5.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BH50" t="n">
         <v>2.78</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G51" t="n">
         <v>2.6</v>
@@ -13312,43 +13312,43 @@
         <v>3.25</v>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J51" t="n">
         <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L51" t="n">
         <v>1.38</v>
       </c>
       <c r="M51" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="O51" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P51" t="n">
         <v>1.62</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R51" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="T51" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U51" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V51" t="n">
         <v>1.33</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
         <v>2.88</v>
       </c>
       <c r="O53" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P53" t="n">
         <v>1.7</v>
@@ -13865,7 +13865,7 @@
         <v>1.22</v>
       </c>
       <c r="X53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y53" t="n">
         <v>8.4</v>
@@ -13877,10 +13877,10 @@
         <v>25</v>
       </c>
       <c r="AB53" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD53" t="n">
         <v>11.5</v>
@@ -13889,88 +13889,88 @@
         <v>25</v>
       </c>
       <c r="AF53" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AG53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH53" t="n">
         <v>23</v>
       </c>
-      <c r="AH53" t="n">
-        <v>25</v>
-      </c>
       <c r="AI53" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ53" t="n">
         <v>900</v>
       </c>
       <c r="AK53" t="n">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="AL53" t="n">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="AM53" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN53" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="AO53" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT53" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="AV53" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AW53" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX53" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AY53" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BA53" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB53" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC53" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF53" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BG53" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH53" t="n">
         <v>3.3</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -14131,10 +14131,10 @@
         <v>1000</v>
       </c>
       <c r="AB54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD54" t="n">
         <v>1000</v>
@@ -14146,7 +14146,7 @@
         <v>1000</v>
       </c>
       <c r="AG54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH54" t="n">
         <v>1000</v>
@@ -14155,10 +14155,10 @@
         <v>1000</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK54" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL54" t="n">
         <v>1000</v>
@@ -14167,64 +14167,64 @@
         <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO54" t="n">
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -14319,40 +14319,40 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="G55" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H55" t="n">
         <v>7.2</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K55" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M55" t="n">
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O55" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P55" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="R55" t="n">
         <v>2.24</v>
@@ -14367,182 +14367,182 @@
         <v>2.44</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W55" t="n">
         <v>1.01</v>
       </c>
       <c r="X55" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y55" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z55" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA55" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB55" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC55" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD55" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF55" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG55" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH55" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK55" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL55" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM55" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN55" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="AO55" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH55" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL55" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN55" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO55" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP55" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR55" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT55" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV55" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX55" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -14636,13 +14636,13 @@
         <v>970</v>
       </c>
       <c r="AA56" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AB56" t="n">
         <v>950</v>
       </c>
       <c r="AC56" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD56" t="n">
         <v>970</v>
@@ -14651,16 +14651,16 @@
         <v>970</v>
       </c>
       <c r="AF56" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AG56" t="n">
         <v>950</v>
       </c>
       <c r="AH56" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI56" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ56" t="n">
         <v>1000</v>
@@ -14669,67 +14669,67 @@
         <v>75</v>
       </c>
       <c r="AL56" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM56" t="n">
         <v>85</v>
       </c>
       <c r="AN56" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AO56" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AP56" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="AS56" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="AV56" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AW56" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX56" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AY56" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA56" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB56" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="BC56" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="BD56" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.1</v>
+        <v>2.16</v>
       </c>
       <c r="BF56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG56" t="n">
         <v>4.5</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>2.96</v>
       </c>
       <c r="G57" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H57" t="n">
         <v>2.46</v>
@@ -14869,7 +14869,7 @@
         <v>3.05</v>
       </c>
       <c r="T57" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U57" t="n">
         <v>2.3</v>
@@ -14878,7 +14878,7 @@
         <v>1.66</v>
       </c>
       <c r="W57" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X57" t="n">
         <v>20</v>
@@ -14896,10 +14896,10 @@
         <v>15.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE57" t="n">
         <v>29</v>
@@ -14917,16 +14917,16 @@
         <v>42</v>
       </c>
       <c r="AJ57" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK57" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AL57" t="n">
         <v>46</v>
       </c>
       <c r="AM57" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN57" t="n">
         <v>32</v>
@@ -14968,7 +14968,7 @@
         <v>15</v>
       </c>
       <c r="BA57" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB57" t="n">
         <v>27</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -15081,13 +15081,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G58" t="n">
         <v>3.15</v>
       </c>
       <c r="H58" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I58" t="n">
         <v>2.34</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -15377,28 +15377,28 @@
         <v>1.92</v>
       </c>
       <c r="T59" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U59" t="n">
         <v>2.96</v>
       </c>
       <c r="V59" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W59" t="n">
         <v>2.24</v>
       </c>
       <c r="X59" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Y59" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Z59" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AA59" t="n">
-        <v>100</v>
+        <v>470</v>
       </c>
       <c r="AB59" t="n">
         <v>22</v>
@@ -15410,7 +15410,7 @@
         <v>24</v>
       </c>
       <c r="AE59" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF59" t="n">
         <v>21</v>
@@ -15422,7 +15422,7 @@
         <v>19</v>
       </c>
       <c r="AI59" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ59" t="n">
         <v>27</v>
@@ -15434,7 +15434,7 @@
         <v>25</v>
       </c>
       <c r="AM59" t="n">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN59" t="n">
         <v>6.8</v>
@@ -15443,55 +15443,55 @@
         <v>27</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT59" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="AU59" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV59" t="n">
         <v>14</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX59" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AY59" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AZ59" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB59" t="n">
-        <v>16</v>
+        <v>3.75</v>
       </c>
       <c r="BC59" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD59" t="n">
-        <v>15</v>
+        <v>3.75</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG59" t="n">
         <v>15.5</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -15589,40 +15589,40 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G60" t="n">
-        <v>8.4</v>
+        <v>2.6</v>
       </c>
       <c r="H60" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>2.7</v>
       </c>
       <c r="K60" t="n">
-        <v>500</v>
+        <v>3.3</v>
       </c>
       <c r="L60" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N60" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="O60" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P60" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R60" t="n">
         <v>1.12</v>
@@ -15631,124 +15631,124 @@
         <v>1.05</v>
       </c>
       <c r="T60" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U60" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="V60" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W60" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y60" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA60" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB60" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AC60" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD60" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE60" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF60" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG60" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AH60" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AI60" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM60" t="n">
         <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO60" t="n">
         <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15927,7 @@
         <v>970</v>
       </c>
       <c r="AH61" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI61" t="n">
         <v>500</v>
@@ -15960,7 +15960,7 @@
         <v>4.2</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.26</v>
+        <v>4.8</v>
       </c>
       <c r="AT61" t="n">
         <v>3.35</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -16097,46 +16097,46 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="G62" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="H62" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="J62" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K62" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="L62" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="M62" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="P62" t="n">
         <v>1.41</v>
       </c>
       <c r="Q62" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S62" t="n">
         <v>3.1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S62" t="n">
-        <v>6.4</v>
       </c>
       <c r="T62" t="n">
         <v>1.11</v>
@@ -16145,10 +16145,10 @@
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W62" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -16351,7 +16351,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G63" t="n">
         <v>1000</v>
@@ -16405,7 +16405,7 @@
         <v>1.25</v>
       </c>
       <c r="X63" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y63" t="n">
         <v>1000</v>
@@ -16459,58 +16459,58 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
         <v>1.74</v>
       </c>
       <c r="I64" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J64" t="n">
         <v>2.14</v>
@@ -16659,7 +16659,7 @@
         <v>1.22</v>
       </c>
       <c r="X64" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y64" t="n">
         <v>1000</v>
@@ -16713,58 +16713,58 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -16871,7 +16871,7 @@
         <v>1000</v>
       </c>
       <c r="J65" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K65" t="n">
         <v>1000</v>
@@ -16967,58 +16967,58 @@
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH65" t="n">
         <v>1000</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -17116,10 +17116,10 @@
         <v>1.68</v>
       </c>
       <c r="G66" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H66" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I66" t="n">
         <v>1000</v>
@@ -17170,109 +17170,109 @@
         <v>950</v>
       </c>
       <c r="Y66" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA66" t="n">
         <v>900</v>
       </c>
       <c r="AB66" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC66" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD66" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH66" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ66" t="n">
         <v>900</v>
       </c>
       <c r="AK66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO66" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BD66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BG66" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BH66" t="n">
         <v>1000</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
         <v>1000</v>
       </c>
       <c r="H67" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="I67" t="n">
         <v>1000</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17627,7 @@
         <v>7.8</v>
       </c>
       <c r="H68" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I68" t="n">
         <v>1000</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -17917,7 +17917,7 @@
         <v>3.8</v>
       </c>
       <c r="T69" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="U69" t="n">
         <v>2.02</v>
@@ -17932,19 +17932,19 @@
         <v>13</v>
       </c>
       <c r="Y69" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z69" t="n">
         <v>15.5</v>
       </c>
       <c r="AA69" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AB69" t="n">
         <v>14</v>
       </c>
       <c r="AC69" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD69" t="n">
         <v>13</v>
@@ -17992,10 +17992,10 @@
         <v>10.5</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT69" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU69" t="n">
         <v>6.6</v>
@@ -18016,22 +18016,22 @@
         <v>16</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB69" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC69" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD69" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE69" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF69" t="n">
         <v>6</v>
-      </c>
-      <c r="BF69" t="n">
-        <v>5.6</v>
       </c>
       <c r="BG69" t="n">
         <v>17.5</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -18129,16 +18129,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G70" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H70" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J70" t="n">
         <v>3.4</v>
@@ -18159,10 +18159,10 @@
         <v>1.3</v>
       </c>
       <c r="P70" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R70" t="n">
         <v>1.4</v>
@@ -18177,10 +18177,10 @@
         <v>2.3</v>
       </c>
       <c r="V70" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W70" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X70" t="n">
         <v>15</v>
@@ -18207,7 +18207,7 @@
         <v>40</v>
       </c>
       <c r="AF70" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG70" t="n">
         <v>11</v>
@@ -18240,7 +18240,7 @@
         <v>13</v>
       </c>
       <c r="AQ70" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR70" t="n">
         <v>22</v>
@@ -18279,7 +18279,7 @@
         <v>21</v>
       </c>
       <c r="BD70" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE70" t="n">
         <v>46</v>
@@ -18288,7 +18288,7 @@
         <v>15</v>
       </c>
       <c r="BG70" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="BH70" t="n">
         <v>1000</v>
@@ -18300,59 +18300,59 @@
         <v>1000</v>
       </c>
       <c r="BK70" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL70" t="n">
         <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN70" t="n">
         <v>1000</v>
       </c>
       <c r="BO70" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP70" t="n">
         <v>1000</v>
       </c>
       <c r="BQ70" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR70" t="n">
         <v>1000</v>
       </c>
       <c r="BS70" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT70" t="n">
         <v>1000</v>
       </c>
       <c r="BU70" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX70" t="n">
         <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ70" t="n">
         <v>1000</v>
       </c>
       <c r="CA70" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
         <v>3.3</v>
       </c>
       <c r="K71" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L71" t="n">
         <v>1.38</v>
@@ -18443,7 +18443,7 @@
         <v>17.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AA71" t="n">
         <v>900</v>
@@ -18458,7 +18458,7 @@
         <v>24</v>
       </c>
       <c r="AE71" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF71" t="n">
         <v>970</v>
@@ -18467,10 +18467,10 @@
         <v>13</v>
       </c>
       <c r="AH71" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI71" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AJ71" t="n">
         <v>900</v>
@@ -18479,16 +18479,16 @@
         <v>65</v>
       </c>
       <c r="AL71" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM71" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN71" t="n">
         <v>970</v>
       </c>
       <c r="AO71" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP71" t="n">
         <v>8.6</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -18640,10 +18640,10 @@
         <v>2.54</v>
       </c>
       <c r="G72" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H72" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I72" t="n">
         <v>3.35</v>
@@ -18682,13 +18682,13 @@
         <v>2.08</v>
       </c>
       <c r="U72" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V72" t="n">
         <v>1.42</v>
       </c>
       <c r="W72" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X72" t="n">
         <v>10.5</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -18894,16 +18894,16 @@
         <v>1.12</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="H73" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
         <v>1000</v>
       </c>
       <c r="J73" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
         <v>1000</v>
@@ -18942,7 +18942,7 @@
         <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -19399,10 +19399,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G75" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H75" t="n">
         <v>4.1</v>
@@ -19429,7 +19429,7 @@
         <v>1.61</v>
       </c>
       <c r="P75" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q75" t="n">
         <v>2.84</v>
@@ -19444,7 +19444,7 @@
         <v>2.28</v>
       </c>
       <c r="U75" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V75" t="n">
         <v>1.29</v>
@@ -19495,7 +19495,7 @@
         <v>65</v>
       </c>
       <c r="AL75" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM75" t="n">
         <v>280</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -19761,58 +19761,58 @@
         <v>1000</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF76" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG76" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH76" t="n">
         <v>1000</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -20173,22 +20173,22 @@
         <v>6.8</v>
       </c>
       <c r="J78" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K78" t="n">
         <v>4.8</v>
       </c>
       <c r="L78" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M78" t="n">
         <v>1.05</v>
       </c>
       <c r="N78" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O78" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P78" t="n">
         <v>2.24</v>
@@ -20206,7 +20206,7 @@
         <v>1.83</v>
       </c>
       <c r="U78" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V78" t="n">
         <v>1.17</v>
@@ -20239,13 +20239,13 @@
         <v>85</v>
       </c>
       <c r="AF78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG78" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH78" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI78" t="n">
         <v>1000</v>
@@ -20278,7 +20278,7 @@
         <v>28</v>
       </c>
       <c r="AS78" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT78" t="n">
         <v>8.800000000000001</v>
@@ -20311,16 +20311,16 @@
         <v>14</v>
       </c>
       <c r="BD78" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE78" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF78" t="n">
         <v>6.8</v>
       </c>
       <c r="BG78" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH78" t="n">
         <v>3.95</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -20415,22 +20415,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="H79" t="n">
         <v>3.4</v>
       </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>2.56</v>
       </c>
       <c r="K79" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L79" t="n">
         <v>1.58</v>
@@ -20439,10 +20439,10 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="O79" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="P79" t="n">
         <v>1.27</v>
@@ -20454,7 +20454,7 @@
         <v>1.12</v>
       </c>
       <c r="S79" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T79" t="n">
         <v>1.11</v>
@@ -20463,10 +20463,10 @@
         <v>1.11</v>
       </c>
       <c r="V79" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W79" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X79" t="n">
         <v>500</v>
@@ -20505,7 +20505,7 @@
         <v>500</v>
       </c>
       <c r="AJ79" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK79" t="n">
         <v>500</v>
@@ -20523,58 +20523,58 @@
         <v>500</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU79" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AV79" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX79" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BA79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF79" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG79" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BH79" t="n">
         <v>1000</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -20684,7 +20684,7 @@
         <v>2.8</v>
       </c>
       <c r="K80" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -20923,7 +20923,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G81" t="n">
         <v>2.3</v>
@@ -20935,10 +20935,10 @@
         <v>4.2</v>
       </c>
       <c r="J81" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K81" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -20974,7 +20974,7 @@
         <v>1.31</v>
       </c>
       <c r="W81" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X81" t="n">
         <v>13</v>
@@ -21019,7 +21019,7 @@
         <v>28</v>
       </c>
       <c r="AL81" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM81" t="n">
         <v>500</v>
@@ -21073,7 +21073,7 @@
         <v>20</v>
       </c>
       <c r="BD81" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE81" t="n">
         <v>8.4</v>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -21192,10 +21192,10 @@
         <v>2.98</v>
       </c>
       <c r="K82" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L82" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M82" t="n">
         <v>1.13</v>
@@ -21207,7 +21207,7 @@
         <v>1.55</v>
       </c>
       <c r="P82" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q82" t="n">
         <v>2.64</v>
@@ -21219,7 +21219,7 @@
         <v>5.5</v>
       </c>
       <c r="T82" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U82" t="n">
         <v>1.81</v>
@@ -21261,7 +21261,7 @@
         <v>14.5</v>
       </c>
       <c r="AH82" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI82" t="n">
         <v>500</v>
@@ -21318,13 +21318,13 @@
         <v>4.6</v>
       </c>
       <c r="BA82" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB82" t="n">
         <v>4.8</v>
       </c>
       <c r="BC82" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD82" t="n">
         <v>5.1</v>
@@ -21339,68 +21339,68 @@
         <v>5.3</v>
       </c>
       <c r="BH82" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI82" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="BJ82" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BK82" t="n">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="BL82" t="n">
         <v>1000</v>
       </c>
       <c r="BM82" t="n">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="BN82" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO82" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP82" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ82" t="n">
-        <v>1.58</v>
+        <v>7.2</v>
       </c>
       <c r="BR82" t="n">
         <v>1000</v>
       </c>
       <c r="BS82" t="n">
-        <v>1.63</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT82" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BU82" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV82" t="n">
         <v>1000</v>
       </c>
       <c r="BW82" t="n">
-        <v>1.62</v>
+        <v>8.4</v>
       </c>
       <c r="BX82" t="n">
         <v>1000</v>
       </c>
       <c r="BY82" t="n">
-        <v>1.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ82" t="n">
         <v>1000</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.63</v>
+        <v>9</v>
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -21434,19 +21434,19 @@
         <v>1.65</v>
       </c>
       <c r="G83" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H83" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I83" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J83" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K83" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L83" t="n">
         <v>1.01</v>
@@ -21458,7 +21458,7 @@
         <v>2.88</v>
       </c>
       <c r="O83" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P83" t="n">
         <v>2.38</v>
@@ -21470,7 +21470,7 @@
         <v>1.52</v>
       </c>
       <c r="S83" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="T83" t="n">
         <v>1.11</v>
@@ -21479,13 +21479,13 @@
         <v>1.11</v>
       </c>
       <c r="V83" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W83" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X83" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y83" t="n">
         <v>1000</v>
@@ -21497,7 +21497,7 @@
         <v>900</v>
       </c>
       <c r="AB83" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AC83" t="n">
         <v>1000</v>
@@ -21512,7 +21512,7 @@
         <v>40</v>
       </c>
       <c r="AG83" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AH83" t="n">
         <v>1000</v>
@@ -21539,58 +21539,58 @@
         <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF83" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BG83" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH83" t="n">
         <v>1000</v>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
         <v>2.5</v>
       </c>
       <c r="H85" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I85" t="n">
         <v>4.5</v>
@@ -21963,7 +21963,7 @@
         <v>1.15</v>
       </c>
       <c r="N85" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O85" t="n">
         <v>1.61</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
